--- a/ig/DM-JUILLET-2025/CodeSystem-TRE-R211-ActiviteOperationnelle.xlsx
+++ b/ig/DM-JUILLET-2025/CodeSystem-TRE-R211-ActiviteOperationnelle.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2030" uniqueCount="1408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2040" uniqueCount="1418">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250623120000</t>
+    <t>20250723120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-23T12:00:00+01:00</t>
+    <t>2025-07-23T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2215,7 +2215,7 @@
     <t>308</t>
   </si>
   <si>
-    <t>Accompagnements à la parentalité</t>
+    <t>Soutien à la parentalité et accompagnement familial</t>
   </si>
   <si>
     <t>309</t>
@@ -2824,6 +2824,9 @@
     <t>Evaluation du logement et préconisation d'adaptation pour le maintien à domicile</t>
   </si>
   <si>
+    <t>Analyse de l’environnement domestique d’une personne en situation de perte d’autonomie, de handicap ou présentant des limitations fonctionnelles, afin d’identifier les obstacles à son maintien à domicile dans des conditions optimales de sécurité, d’autonomie et de qualité de vie. Elle vise à préconiser des aménagements et des aides techniques adaptés, permettant à la personne de réaliser ses activités quotidiennes dans un cadre sécurisé. Cette orientation est étayée par la réalisation de formations continues spécifiques auprès de cette population (appuyées de données probantes) et d’une expérience professionnelle</t>
+  </si>
+  <si>
     <t>402</t>
   </si>
   <si>
@@ -4024,6 +4027,9 @@
     <t>Ergothérapie</t>
   </si>
   <si>
+    <t>Activité professionelle qui contribue, par la rééducation, la réadaptation et la réinsertion, au traitement des déficiences, des incapacités et des situations de handicap</t>
+  </si>
+  <si>
     <t>559</t>
   </si>
   <si>
@@ -4120,46 +4126,70 @@
     <t>Ergothérapie orientation accompagnement dans le cadre des maladies chroniques</t>
   </si>
   <si>
+    <t>Accompagnement en ergothérapie centré sur l’impact de maladies chroniques (affection de longue durée qui évolue dans le temps, souvent lentement, et qui a un impact durable sur la vie quotidienne de la personne) dans le quotidien de la personne : gestion de la fatigue et/ou la gestion de la douleur et/ou la gestion du sommeil en lien avec les activités de vie la personne dans son environnement. Il vise à favoriser la qualité de vie, l’équilibre de vie.</t>
+  </si>
+  <si>
     <t>575</t>
   </si>
   <si>
     <t>Ergothérapie orientation compensation matérielle dans l’environnement de la personne</t>
   </si>
   <si>
+    <t>Accompagnement en ergothérapie de personnes dans l’accès à l'ensemble des aides techniques, équipements et aménagements destinés à compenser une perte de fonction, une limitation d’activité ou une situation de handicap. Cela inclus l’apprentissage d’utilisation des compensations matérielles et la prise en compte de l’environnement de la personne jusqu’à intervenir dans celui-ci.</t>
+  </si>
+  <si>
     <t>576</t>
   </si>
   <si>
     <t>Ergothérapie orientation Gériatrie</t>
   </si>
   <si>
+    <t>Accompagnement en ergothérapie concerne la prise en charge des personnes âgées, notamment celles confrontées à des pertes d’autonomie, des pathologies chroniques ou neurodégénératives (comme la maladie d'Alzheimer, Parkinson, ou des troubles cognitifs), ainsi qu'à la prévention du vieillissement pathologique. Cette orientation est étayée par la réalisation de formations continues spécifiques auprès de cette population (appuyées de données probantes) et d’une expérience professionnelle</t>
+  </si>
+  <si>
     <t>577</t>
   </si>
   <si>
     <t>Ergothérapie orientation Neurologie</t>
   </si>
   <si>
+    <t>Accompagnement en ergothérapie auprès de personnes avec des pathologies neurologiques innées ou acquises (dépistage ; repérage ; évaluation permettant le diagnostic ergothérapique ; réévaluation). Cette orientation est étayée par la réalisation de formations continues spécifiques auprès de cette population (appuyées de données probantes) et d’une expérience professionnelle.</t>
+  </si>
+  <si>
     <t>578</t>
   </si>
   <si>
     <t>Ergothérapie orientation Pédiatrie</t>
   </si>
   <si>
+    <t>Accompagnement en ergothérapie des enfants, de la naissance à l’adolescence, présentant des troubles du développement, des déficiences physiques, sensorielles, cognitives ou psychiques, ainsi que des situations de handicap, afin de favoriser leur autonomie et leur participation dans les activités de la vie quotidienne, scolaire et sociale. Cette orientation est étayée par la réalisation de formations continues spécifiques auprès de cette population (appuyées de données probantes) et d’une expérience professionnelle.</t>
+  </si>
+  <si>
     <t>579</t>
   </si>
   <si>
     <t>Ergothérapie orientation Psychiatrie et Santé mentale</t>
   </si>
   <si>
+    <t>Accompagnement en ergothérapie  concerne l’accompagnement des personnes présentant des troubles psychiques ou psychiatriques afin de favoriser leur autonomie, leur bien-être et leur inclusion sociale. L’ergothérapeute intervient en évaluant et en renforçant les capacités fonctionnelles, cognitives, émotionnelles et sociales des patients dans le cadre d’un projet thérapeutique global. Cette orientation est étayée par la réalisation de formations continues spécifiques auprès de cette population (appuyées de données probantes) et d’une expérience professionnelle</t>
+  </si>
+  <si>
     <t>580</t>
   </si>
   <si>
     <t>Evaluation en ergothérapie par l’analyse d’activité et accompagnement dans l’environnement de la personne</t>
   </si>
   <si>
+    <t>Evaluation fonctionnelle et accompagnement en ergothérapie au travers de mises en situation d’activité réelles (via l’analyse d’activité) en milieu écologique (sur l’ensemble des lieux de vie ((domicile, établissements médico-sociaux, etc.) et d’activité de la personne (établissements scolaires, lieux de formation, milieu professionnel, milieu sportif, de loisirs, etc.)</t>
+  </si>
+  <si>
     <t>581</t>
   </si>
   <si>
     <t>Interventions éducatives pour renforcer l’autorégulation</t>
+  </si>
+  <si>
+    <t>Consiste à mettre en place des stratégies et des activités visant à aider les personnes, notamment les enfants et les adolescents, à mieux gérer leurs émotions, leurs comportements et leurs pensées. Ces interventions sont particulièrement utiles pour les élèves présentant des troubles du spectre de l'autisme (TSA) et d'autres troubles du neurodéveloppement. Elles sont encadrées par des professionnels, et s'appuient sur des principes de métacognition et d'autodétermination. Cette orientation est étayée par la réalisation de formations continues spécifiques auprès de cette population (appuyées de données probantes) et d’une expérience professionnelle</t>
   </si>
   <si>
     <t>582</t>
@@ -9640,20 +9670,22 @@
       <c r="C402" t="s" s="2">
         <v>935</v>
       </c>
-      <c r="D402" s="2"/>
+      <c r="D402" t="s" s="2">
+        <v>936</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="s" s="2">
         <v>58</v>
       </c>
       <c r="B403" t="s" s="2">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="C403" t="s" s="2">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="D403" t="s" s="2">
-        <v>938</v>
+        <v>939</v>
       </c>
     </row>
     <row r="404">
@@ -9661,10 +9693,10 @@
         <v>58</v>
       </c>
       <c r="B404" t="s" s="2">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="C404" t="s" s="2">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="D404" s="2"/>
     </row>
@@ -9673,13 +9705,13 @@
         <v>58</v>
       </c>
       <c r="B405" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="C405" t="s" s="2">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="D405" t="s" s="2">
-        <v>943</v>
+        <v>944</v>
       </c>
     </row>
     <row r="406">
@@ -9687,10 +9719,10 @@
         <v>58</v>
       </c>
       <c r="B406" t="s" s="2">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="C406" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="D406" s="2"/>
     </row>
@@ -9699,10 +9731,10 @@
         <v>58</v>
       </c>
       <c r="B407" t="s" s="2">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="C407" t="s" s="2">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="D407" s="2"/>
     </row>
@@ -9711,10 +9743,10 @@
         <v>58</v>
       </c>
       <c r="B408" t="s" s="2">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="C408" t="s" s="2">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="D408" s="2"/>
     </row>
@@ -9723,10 +9755,10 @@
         <v>58</v>
       </c>
       <c r="B409" t="s" s="2">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="C409" t="s" s="2">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="D409" s="2"/>
     </row>
@@ -9735,13 +9767,13 @@
         <v>58</v>
       </c>
       <c r="B410" t="s" s="2">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="C410" t="s" s="2">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="D410" t="s" s="2">
-        <v>954</v>
+        <v>955</v>
       </c>
     </row>
     <row r="411">
@@ -9749,13 +9781,13 @@
         <v>58</v>
       </c>
       <c r="B411" t="s" s="2">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="C411" t="s" s="2">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="D411" t="s" s="2">
-        <v>957</v>
+        <v>958</v>
       </c>
     </row>
     <row r="412">
@@ -9763,10 +9795,10 @@
         <v>58</v>
       </c>
       <c r="B412" t="s" s="2">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="C412" t="s" s="2">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="D412" s="2"/>
     </row>
@@ -9775,10 +9807,10 @@
         <v>58</v>
       </c>
       <c r="B413" t="s" s="2">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="C413" t="s" s="2">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="D413" s="2"/>
     </row>
@@ -9787,10 +9819,10 @@
         <v>58</v>
       </c>
       <c r="B414" t="s" s="2">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C414" t="s" s="2">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="D414" s="2"/>
     </row>
@@ -9799,10 +9831,10 @@
         <v>58</v>
       </c>
       <c r="B415" t="s" s="2">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="C415" t="s" s="2">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="D415" s="2"/>
     </row>
@@ -9811,10 +9843,10 @@
         <v>58</v>
       </c>
       <c r="B416" t="s" s="2">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="C416" t="s" s="2">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="D416" s="2"/>
     </row>
@@ -9823,10 +9855,10 @@
         <v>58</v>
       </c>
       <c r="B417" t="s" s="2">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C417" t="s" s="2">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="D417" s="2"/>
     </row>
@@ -9835,10 +9867,10 @@
         <v>58</v>
       </c>
       <c r="B418" t="s" s="2">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="C418" t="s" s="2">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="D418" s="2"/>
     </row>
@@ -9847,10 +9879,10 @@
         <v>58</v>
       </c>
       <c r="B419" t="s" s="2">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="C419" t="s" s="2">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="D419" s="2"/>
     </row>
@@ -9859,10 +9891,10 @@
         <v>58</v>
       </c>
       <c r="B420" t="s" s="2">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C420" t="s" s="2">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="D420" s="2"/>
     </row>
@@ -9871,10 +9903,10 @@
         <v>58</v>
       </c>
       <c r="B421" t="s" s="2">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="C421" t="s" s="2">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="D421" s="2"/>
     </row>
@@ -9883,10 +9915,10 @@
         <v>58</v>
       </c>
       <c r="B422" t="s" s="2">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="C422" t="s" s="2">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="D422" s="2"/>
     </row>
@@ -9895,10 +9927,10 @@
         <v>58</v>
       </c>
       <c r="B423" t="s" s="2">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="C423" t="s" s="2">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="D423" s="2"/>
     </row>
@@ -9907,10 +9939,10 @@
         <v>58</v>
       </c>
       <c r="B424" t="s" s="2">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="C424" t="s" s="2">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="D424" s="2"/>
     </row>
@@ -9919,10 +9951,10 @@
         <v>58</v>
       </c>
       <c r="B425" t="s" s="2">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="C425" t="s" s="2">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="D425" s="2"/>
     </row>
@@ -9931,10 +9963,10 @@
         <v>58</v>
       </c>
       <c r="B426" t="s" s="2">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="C426" t="s" s="2">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="D426" s="2"/>
     </row>
@@ -9943,10 +9975,10 @@
         <v>58</v>
       </c>
       <c r="B427" t="s" s="2">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="C427" t="s" s="2">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="D427" s="2"/>
     </row>
@@ -9955,10 +9987,10 @@
         <v>58</v>
       </c>
       <c r="B428" t="s" s="2">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="C428" t="s" s="2">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="D428" s="2"/>
     </row>
@@ -9967,10 +9999,10 @@
         <v>58</v>
       </c>
       <c r="B429" t="s" s="2">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="C429" t="s" s="2">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D429" s="2"/>
     </row>
@@ -9979,10 +10011,10 @@
         <v>58</v>
       </c>
       <c r="B430" t="s" s="2">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="C430" t="s" s="2">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="D430" s="2"/>
     </row>
@@ -9991,10 +10023,10 @@
         <v>58</v>
       </c>
       <c r="B431" t="s" s="2">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="C431" t="s" s="2">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="D431" s="2"/>
     </row>
@@ -10003,10 +10035,10 @@
         <v>58</v>
       </c>
       <c r="B432" t="s" s="2">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="C432" t="s" s="2">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="D432" s="2"/>
     </row>
@@ -10015,10 +10047,10 @@
         <v>58</v>
       </c>
       <c r="B433" t="s" s="2">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="C433" t="s" s="2">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="D433" s="2"/>
     </row>
@@ -10027,10 +10059,10 @@
         <v>58</v>
       </c>
       <c r="B434" t="s" s="2">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="C434" t="s" s="2">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="D434" s="2"/>
     </row>
@@ -10039,13 +10071,13 @@
         <v>58</v>
       </c>
       <c r="B435" t="s" s="2">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="C435" t="s" s="2">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="D435" t="s" s="2">
-        <v>1006</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="436">
@@ -10053,13 +10085,13 @@
         <v>58</v>
       </c>
       <c r="B436" t="s" s="2">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="C436" t="s" s="2">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="D436" t="s" s="2">
-        <v>1009</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="437">
@@ -10067,10 +10099,10 @@
         <v>58</v>
       </c>
       <c r="B437" t="s" s="2">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="C437" t="s" s="2">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="D437" s="2"/>
     </row>
@@ -10079,13 +10111,13 @@
         <v>58</v>
       </c>
       <c r="B438" t="s" s="2">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="C438" t="s" s="2">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="D438" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="439">
@@ -10093,10 +10125,10 @@
         <v>58</v>
       </c>
       <c r="B439" t="s" s="2">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="C439" t="s" s="2">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="D439" s="2"/>
     </row>
@@ -10105,13 +10137,13 @@
         <v>58</v>
       </c>
       <c r="B440" t="s" s="2">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="C440" t="s" s="2">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="D440" t="s" s="2">
-        <v>1019</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="441">
@@ -10119,13 +10151,13 @@
         <v>58</v>
       </c>
       <c r="B441" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="C441" t="s" s="2">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="D441" t="s" s="2">
-        <v>1022</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="442">
@@ -10133,13 +10165,13 @@
         <v>58</v>
       </c>
       <c r="B442" t="s" s="2">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="C442" t="s" s="2">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="D442" t="s" s="2">
-        <v>1025</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="443">
@@ -10147,13 +10179,13 @@
         <v>58</v>
       </c>
       <c r="B443" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="C443" t="s" s="2">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="D443" t="s" s="2">
-        <v>1028</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="444">
@@ -10161,13 +10193,13 @@
         <v>58</v>
       </c>
       <c r="B444" t="s" s="2">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="C444" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="D444" t="s" s="2">
-        <v>1031</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="445">
@@ -10175,13 +10207,13 @@
         <v>58</v>
       </c>
       <c r="B445" t="s" s="2">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="C445" t="s" s="2">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="D445" t="s" s="2">
-        <v>1034</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="446">
@@ -10189,13 +10221,13 @@
         <v>58</v>
       </c>
       <c r="B446" t="s" s="2">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="C446" t="s" s="2">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="D446" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="447">
@@ -10203,13 +10235,13 @@
         <v>58</v>
       </c>
       <c r="B447" t="s" s="2">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="C447" t="s" s="2">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="D447" t="s" s="2">
-        <v>1040</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="448">
@@ -10217,13 +10249,13 @@
         <v>58</v>
       </c>
       <c r="B448" t="s" s="2">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C448" t="s" s="2">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="D448" t="s" s="2">
-        <v>1043</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="449">
@@ -10231,13 +10263,13 @@
         <v>58</v>
       </c>
       <c r="B449" t="s" s="2">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="C449" t="s" s="2">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="D449" t="s" s="2">
-        <v>1046</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="450">
@@ -10245,13 +10277,13 @@
         <v>58</v>
       </c>
       <c r="B450" t="s" s="2">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="C450" t="s" s="2">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="D450" t="s" s="2">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="451">
@@ -10259,13 +10291,13 @@
         <v>58</v>
       </c>
       <c r="B451" t="s" s="2">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="C451" t="s" s="2">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="D451" t="s" s="2">
-        <v>1052</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="452">
@@ -10273,13 +10305,13 @@
         <v>58</v>
       </c>
       <c r="B452" t="s" s="2">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="C452" t="s" s="2">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="D452" t="s" s="2">
-        <v>1055</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="453">
@@ -10287,13 +10319,13 @@
         <v>58</v>
       </c>
       <c r="B453" t="s" s="2">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="C453" t="s" s="2">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="D453" t="s" s="2">
-        <v>1058</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="454">
@@ -10301,10 +10333,10 @@
         <v>58</v>
       </c>
       <c r="B454" t="s" s="2">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="C454" t="s" s="2">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="D454" s="2"/>
     </row>
@@ -10313,13 +10345,13 @@
         <v>58</v>
       </c>
       <c r="B455" t="s" s="2">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="C455" t="s" s="2">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="D455" t="s" s="2">
-        <v>1063</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="456">
@@ -10327,13 +10359,13 @@
         <v>58</v>
       </c>
       <c r="B456" t="s" s="2">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="C456" t="s" s="2">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="D456" t="s" s="2">
-        <v>1066</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="457">
@@ -10341,13 +10373,13 @@
         <v>58</v>
       </c>
       <c r="B457" t="s" s="2">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="C457" t="s" s="2">
         <v>568</v>
       </c>
       <c r="D457" t="s" s="2">
-        <v>1068</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="458">
@@ -10355,10 +10387,10 @@
         <v>58</v>
       </c>
       <c r="B458" t="s" s="2">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="C458" t="s" s="2">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="D458" s="2"/>
     </row>
@@ -10367,7 +10399,7 @@
         <v>58</v>
       </c>
       <c r="B459" t="s" s="2">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="C459" t="s" s="2">
         <v>574</v>
@@ -10381,7 +10413,7 @@
         <v>58</v>
       </c>
       <c r="B460" t="s" s="2">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="C460" t="s" s="2">
         <v>571</v>
@@ -10395,10 +10427,10 @@
         <v>58</v>
       </c>
       <c r="B461" t="s" s="2">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="C461" t="s" s="2">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="D461" t="s" s="2">
         <v>572</v>
@@ -10409,7 +10441,7 @@
         <v>58</v>
       </c>
       <c r="B462" t="s" s="2">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C462" t="s" s="2">
         <v>580</v>
@@ -10423,7 +10455,7 @@
         <v>58</v>
       </c>
       <c r="B463" t="s" s="2">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="C463" t="s" s="2">
         <v>576</v>
@@ -10437,10 +10469,10 @@
         <v>58</v>
       </c>
       <c r="B464" t="s" s="2">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C464" t="s" s="2">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="D464" t="s" s="2">
         <v>572</v>
@@ -10451,10 +10483,10 @@
         <v>58</v>
       </c>
       <c r="B465" t="s" s="2">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="C465" t="s" s="2">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="D465" t="s" s="2">
         <v>572</v>
@@ -10465,10 +10497,10 @@
         <v>58</v>
       </c>
       <c r="B466" t="s" s="2">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="C466" t="s" s="2">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="D466" t="s" s="2">
         <v>572</v>
@@ -10479,13 +10511,13 @@
         <v>58</v>
       </c>
       <c r="B467" t="s" s="2">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="C467" t="s" s="2">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="D467" t="s" s="2">
-        <v>1085</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="468">
@@ -10493,13 +10525,13 @@
         <v>58</v>
       </c>
       <c r="B468" t="s" s="2">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="C468" t="s" s="2">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="D468" t="s" s="2">
-        <v>1088</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="469">
@@ -10507,13 +10539,13 @@
         <v>58</v>
       </c>
       <c r="B469" t="s" s="2">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="C469" t="s" s="2">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="D469" t="s" s="2">
-        <v>1091</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="470">
@@ -10521,13 +10553,13 @@
         <v>58</v>
       </c>
       <c r="B470" t="s" s="2">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="C470" t="s" s="2">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="D470" t="s" s="2">
-        <v>1094</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="471">
@@ -10535,13 +10567,13 @@
         <v>58</v>
       </c>
       <c r="B471" t="s" s="2">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="C471" t="s" s="2">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="D471" t="s" s="2">
-        <v>1097</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="472">
@@ -10549,13 +10581,13 @@
         <v>58</v>
       </c>
       <c r="B472" t="s" s="2">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="C472" t="s" s="2">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="D472" t="s" s="2">
-        <v>1100</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="473">
@@ -10563,13 +10595,13 @@
         <v>58</v>
       </c>
       <c r="B473" t="s" s="2">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="C473" t="s" s="2">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="D473" t="s" s="2">
-        <v>1103</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="474">
@@ -10577,13 +10609,13 @@
         <v>58</v>
       </c>
       <c r="B474" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="C474" t="s" s="2">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="D474" t="s" s="2">
-        <v>1106</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="475">
@@ -10591,13 +10623,13 @@
         <v>58</v>
       </c>
       <c r="B475" t="s" s="2">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="C475" t="s" s="2">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="D475" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="476">
@@ -10605,13 +10637,13 @@
         <v>58</v>
       </c>
       <c r="B476" t="s" s="2">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="C476" t="s" s="2">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="D476" t="s" s="2">
-        <v>1112</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="477">
@@ -10619,13 +10651,13 @@
         <v>58</v>
       </c>
       <c r="B477" t="s" s="2">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="C477" t="s" s="2">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D477" t="s" s="2">
-        <v>1115</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="478">
@@ -10633,13 +10665,13 @@
         <v>58</v>
       </c>
       <c r="B478" t="s" s="2">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="C478" t="s" s="2">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="D478" t="s" s="2">
-        <v>1118</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="479">
@@ -10647,13 +10679,13 @@
         <v>58</v>
       </c>
       <c r="B479" t="s" s="2">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="C479" t="s" s="2">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="D479" t="s" s="2">
-        <v>1121</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="480">
@@ -10661,10 +10693,10 @@
         <v>58</v>
       </c>
       <c r="B480" t="s" s="2">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="C480" t="s" s="2">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="D480" t="s" s="2">
         <v>823</v>
@@ -10675,13 +10707,13 @@
         <v>58</v>
       </c>
       <c r="B481" t="s" s="2">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="C481" t="s" s="2">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="D481" t="s" s="2">
-        <v>1126</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="482">
@@ -10689,13 +10721,13 @@
         <v>58</v>
       </c>
       <c r="B482" t="s" s="2">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="C482" t="s" s="2">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="D482" t="s" s="2">
-        <v>1129</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="483">
@@ -10703,13 +10735,13 @@
         <v>58</v>
       </c>
       <c r="B483" t="s" s="2">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="C483" t="s" s="2">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="D483" t="s" s="2">
-        <v>1132</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="484">
@@ -10717,13 +10749,13 @@
         <v>58</v>
       </c>
       <c r="B484" t="s" s="2">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="C484" t="s" s="2">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="D484" t="s" s="2">
-        <v>1135</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="485">
@@ -10731,13 +10763,13 @@
         <v>58</v>
       </c>
       <c r="B485" t="s" s="2">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="C485" t="s" s="2">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="D485" t="s" s="2">
-        <v>1138</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="486">
@@ -10745,13 +10777,13 @@
         <v>58</v>
       </c>
       <c r="B486" t="s" s="2">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="C486" t="s" s="2">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="D486" t="s" s="2">
-        <v>1141</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="487">
@@ -10759,13 +10791,13 @@
         <v>58</v>
       </c>
       <c r="B487" t="s" s="2">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="C487" t="s" s="2">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="D487" t="s" s="2">
-        <v>1144</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="488">
@@ -10773,13 +10805,13 @@
         <v>58</v>
       </c>
       <c r="B488" t="s" s="2">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="C488" t="s" s="2">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="D488" t="s" s="2">
-        <v>1147</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="489">
@@ -10787,13 +10819,13 @@
         <v>58</v>
       </c>
       <c r="B489" t="s" s="2">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="C489" t="s" s="2">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="D489" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="490">
@@ -10801,13 +10833,13 @@
         <v>58</v>
       </c>
       <c r="B490" t="s" s="2">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="C490" t="s" s="2">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="D490" t="s" s="2">
-        <v>1153</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="491">
@@ -10815,13 +10847,13 @@
         <v>58</v>
       </c>
       <c r="B491" t="s" s="2">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="C491" t="s" s="2">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="D491" t="s" s="2">
-        <v>1156</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="492">
@@ -10829,10 +10861,10 @@
         <v>58</v>
       </c>
       <c r="B492" t="s" s="2">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="C492" t="s" s="2">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="D492" s="2"/>
     </row>
@@ -10841,13 +10873,13 @@
         <v>58</v>
       </c>
       <c r="B493" t="s" s="2">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="C493" t="s" s="2">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="D493" t="s" s="2">
-        <v>1161</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="494">
@@ -10855,13 +10887,13 @@
         <v>58</v>
       </c>
       <c r="B494" t="s" s="2">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="C494" t="s" s="2">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="D494" t="s" s="2">
-        <v>1164</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="495">
@@ -10869,13 +10901,13 @@
         <v>58</v>
       </c>
       <c r="B495" t="s" s="2">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="C495" t="s" s="2">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="D495" t="s" s="2">
-        <v>1167</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="496">
@@ -10883,13 +10915,13 @@
         <v>58</v>
       </c>
       <c r="B496" t="s" s="2">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="C496" t="s" s="2">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="D496" t="s" s="2">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="497">
@@ -10897,13 +10929,13 @@
         <v>58</v>
       </c>
       <c r="B497" t="s" s="2">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C497" t="s" s="2">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="D497" t="s" s="2">
-        <v>1173</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="498">
@@ -10911,13 +10943,13 @@
         <v>58</v>
       </c>
       <c r="B498" t="s" s="2">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="C498" t="s" s="2">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="D498" t="s" s="2">
-        <v>1176</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="499">
@@ -10925,13 +10957,13 @@
         <v>58</v>
       </c>
       <c r="B499" t="s" s="2">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="C499" t="s" s="2">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="D499" t="s" s="2">
-        <v>1179</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="500">
@@ -10939,10 +10971,10 @@
         <v>58</v>
       </c>
       <c r="B500" t="s" s="2">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="C500" t="s" s="2">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="D500" s="2"/>
     </row>
@@ -10951,13 +10983,13 @@
         <v>58</v>
       </c>
       <c r="B501" t="s" s="2">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="C501" t="s" s="2">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="D501" t="s" s="2">
-        <v>1184</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="502">
@@ -10965,13 +10997,13 @@
         <v>58</v>
       </c>
       <c r="B502" t="s" s="2">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C502" t="s" s="2">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="D502" t="s" s="2">
-        <v>1187</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="503">
@@ -10979,13 +11011,13 @@
         <v>58</v>
       </c>
       <c r="B503" t="s" s="2">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="C503" t="s" s="2">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="D503" t="s" s="2">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="504">
@@ -10993,13 +11025,13 @@
         <v>58</v>
       </c>
       <c r="B504" t="s" s="2">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="C504" t="s" s="2">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="D504" t="s" s="2">
-        <v>1193</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="505">
@@ -11007,13 +11039,13 @@
         <v>58</v>
       </c>
       <c r="B505" t="s" s="2">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="C505" t="s" s="2">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="D505" t="s" s="2">
-        <v>1196</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="506">
@@ -11021,13 +11053,13 @@
         <v>58</v>
       </c>
       <c r="B506" t="s" s="2">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="C506" t="s" s="2">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="D506" t="s" s="2">
-        <v>1199</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="507">
@@ -11035,13 +11067,13 @@
         <v>58</v>
       </c>
       <c r="B507" t="s" s="2">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="C507" t="s" s="2">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="D507" t="s" s="2">
-        <v>1202</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="508">
@@ -11049,13 +11081,13 @@
         <v>58</v>
       </c>
       <c r="B508" t="s" s="2">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="C508" t="s" s="2">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="D508" t="s" s="2">
-        <v>1205</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="509">
@@ -11063,13 +11095,13 @@
         <v>58</v>
       </c>
       <c r="B509" t="s" s="2">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="C509" t="s" s="2">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="D509" t="s" s="2">
-        <v>1208</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="510">
@@ -11077,13 +11109,13 @@
         <v>58</v>
       </c>
       <c r="B510" t="s" s="2">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="C510" t="s" s="2">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="D510" t="s" s="2">
-        <v>1211</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="511">
@@ -11091,13 +11123,13 @@
         <v>58</v>
       </c>
       <c r="B511" t="s" s="2">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="C511" t="s" s="2">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="D511" t="s" s="2">
-        <v>1214</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="512">
@@ -11105,13 +11137,13 @@
         <v>58</v>
       </c>
       <c r="B512" t="s" s="2">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="C512" t="s" s="2">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="D512" t="s" s="2">
-        <v>1217</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="513">
@@ -11119,13 +11151,13 @@
         <v>58</v>
       </c>
       <c r="B513" t="s" s="2">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="C513" t="s" s="2">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="D513" t="s" s="2">
-        <v>1220</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="514">
@@ -11133,10 +11165,10 @@
         <v>58</v>
       </c>
       <c r="B514" t="s" s="2">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="C514" t="s" s="2">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="D514" s="2"/>
     </row>
@@ -11145,10 +11177,10 @@
         <v>58</v>
       </c>
       <c r="B515" t="s" s="2">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="C515" t="s" s="2">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="D515" s="2"/>
     </row>
@@ -11157,10 +11189,10 @@
         <v>58</v>
       </c>
       <c r="B516" t="s" s="2">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="C516" t="s" s="2">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="D516" s="2"/>
     </row>
@@ -11169,10 +11201,10 @@
         <v>58</v>
       </c>
       <c r="B517" t="s" s="2">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="C517" t="s" s="2">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="D517" s="2"/>
     </row>
@@ -11181,10 +11213,10 @@
         <v>58</v>
       </c>
       <c r="B518" t="s" s="2">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="C518" t="s" s="2">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="D518" s="2"/>
     </row>
@@ -11193,10 +11225,10 @@
         <v>58</v>
       </c>
       <c r="B519" t="s" s="2">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="C519" t="s" s="2">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="D519" s="2"/>
     </row>
@@ -11205,13 +11237,13 @@
         <v>58</v>
       </c>
       <c r="B520" t="s" s="2">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="C520" t="s" s="2">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="D520" t="s" s="2">
-        <v>1235</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="521">
@@ -11219,13 +11251,13 @@
         <v>58</v>
       </c>
       <c r="B521" t="s" s="2">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="C521" t="s" s="2">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="D521" t="s" s="2">
-        <v>1238</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="522">
@@ -11233,10 +11265,10 @@
         <v>58</v>
       </c>
       <c r="B522" t="s" s="2">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="C522" t="s" s="2">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="D522" s="2"/>
     </row>
@@ -11245,13 +11277,13 @@
         <v>58</v>
       </c>
       <c r="B523" t="s" s="2">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="C523" t="s" s="2">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="D523" t="s" s="2">
-        <v>1243</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="524">
@@ -11259,10 +11291,10 @@
         <v>58</v>
       </c>
       <c r="B524" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="C524" t="s" s="2">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="D524" s="2"/>
     </row>
@@ -11271,10 +11303,10 @@
         <v>58</v>
       </c>
       <c r="B525" t="s" s="2">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C525" t="s" s="2">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="D525" s="2"/>
     </row>
@@ -11283,10 +11315,10 @@
         <v>58</v>
       </c>
       <c r="B526" t="s" s="2">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="C526" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="D526" s="2"/>
     </row>
@@ -11295,10 +11327,10 @@
         <v>58</v>
       </c>
       <c r="B527" t="s" s="2">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="C527" t="s" s="2">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="D527" s="2"/>
     </row>
@@ -11307,13 +11339,13 @@
         <v>58</v>
       </c>
       <c r="B528" t="s" s="2">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="C528" t="s" s="2">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="D528" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="529">
@@ -11321,13 +11353,13 @@
         <v>58</v>
       </c>
       <c r="B529" t="s" s="2">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="C529" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="D529" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="530">
@@ -11335,13 +11367,13 @@
         <v>58</v>
       </c>
       <c r="B530" t="s" s="2">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="C530" t="s" s="2">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="D530" t="s" s="2">
-        <v>1260</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="531">
@@ -11349,13 +11381,13 @@
         <v>58</v>
       </c>
       <c r="B531" t="s" s="2">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="C531" t="s" s="2">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="D531" t="s" s="2">
-        <v>1263</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="532">
@@ -11363,13 +11395,13 @@
         <v>58</v>
       </c>
       <c r="B532" t="s" s="2">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="C532" t="s" s="2">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="D532" t="s" s="2">
-        <v>1266</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="533">
@@ -11377,13 +11409,13 @@
         <v>58</v>
       </c>
       <c r="B533" t="s" s="2">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="C533" t="s" s="2">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="D533" t="s" s="2">
-        <v>1269</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="534">
@@ -11391,10 +11423,10 @@
         <v>58</v>
       </c>
       <c r="B534" t="s" s="2">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="C534" t="s" s="2">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="D534" s="2"/>
     </row>
@@ -11403,10 +11435,10 @@
         <v>58</v>
       </c>
       <c r="B535" t="s" s="2">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="C535" t="s" s="2">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="D535" s="2"/>
     </row>
@@ -11415,13 +11447,13 @@
         <v>58</v>
       </c>
       <c r="B536" t="s" s="2">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="C536" t="s" s="2">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="D536" t="s" s="2">
-        <v>1276</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="537">
@@ -11429,13 +11461,13 @@
         <v>58</v>
       </c>
       <c r="B537" t="s" s="2">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="C537" t="s" s="2">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="D537" t="s" s="2">
-        <v>1279</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="538">
@@ -11443,13 +11475,13 @@
         <v>58</v>
       </c>
       <c r="B538" t="s" s="2">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="C538" t="s" s="2">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="D538" t="s" s="2">
-        <v>1282</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="539">
@@ -11457,13 +11489,13 @@
         <v>58</v>
       </c>
       <c r="B539" t="s" s="2">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="C539" t="s" s="2">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="D539" t="s" s="2">
-        <v>1285</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="540">
@@ -11471,13 +11503,13 @@
         <v>58</v>
       </c>
       <c r="B540" t="s" s="2">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="C540" t="s" s="2">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="D540" t="s" s="2">
-        <v>1288</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="541">
@@ -11485,13 +11517,13 @@
         <v>58</v>
       </c>
       <c r="B541" t="s" s="2">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="C541" t="s" s="2">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="D541" t="s" s="2">
-        <v>1291</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="542">
@@ -11499,13 +11531,13 @@
         <v>58</v>
       </c>
       <c r="B542" t="s" s="2">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="C542" t="s" s="2">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="D542" t="s" s="2">
-        <v>1294</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="543">
@@ -11513,13 +11545,13 @@
         <v>58</v>
       </c>
       <c r="B543" t="s" s="2">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="C543" t="s" s="2">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="D543" t="s" s="2">
-        <v>1297</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="544">
@@ -11527,13 +11559,13 @@
         <v>58</v>
       </c>
       <c r="B544" t="s" s="2">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C544" t="s" s="2">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="D544" t="s" s="2">
-        <v>1300</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="545">
@@ -11541,13 +11573,13 @@
         <v>58</v>
       </c>
       <c r="B545" t="s" s="2">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="C545" t="s" s="2">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="D545" t="s" s="2">
-        <v>1303</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="546">
@@ -11555,10 +11587,10 @@
         <v>58</v>
       </c>
       <c r="B546" t="s" s="2">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="C546" t="s" s="2">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="D546" s="2"/>
     </row>
@@ -11567,13 +11599,13 @@
         <v>58</v>
       </c>
       <c r="B547" t="s" s="2">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="C547" t="s" s="2">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="D547" t="s" s="2">
-        <v>1308</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="548">
@@ -11581,10 +11613,10 @@
         <v>58</v>
       </c>
       <c r="B548" t="s" s="2">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="C548" t="s" s="2">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="D548" s="2"/>
     </row>
@@ -11593,10 +11625,10 @@
         <v>58</v>
       </c>
       <c r="B549" t="s" s="2">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="C549" t="s" s="2">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="D549" s="2"/>
     </row>
@@ -11605,13 +11637,13 @@
         <v>58</v>
       </c>
       <c r="B550" t="s" s="2">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="C550" t="s" s="2">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="D550" t="s" s="2">
-        <v>1315</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="551">
@@ -11619,10 +11651,10 @@
         <v>58</v>
       </c>
       <c r="B551" t="s" s="2">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="C551" t="s" s="2">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="D551" s="2"/>
     </row>
@@ -11631,10 +11663,10 @@
         <v>58</v>
       </c>
       <c r="B552" t="s" s="2">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="C552" t="s" s="2">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="D552" s="2"/>
     </row>
@@ -11643,10 +11675,10 @@
         <v>58</v>
       </c>
       <c r="B553" t="s" s="2">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="C553" t="s" s="2">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="D553" s="2"/>
     </row>
@@ -11655,10 +11687,10 @@
         <v>58</v>
       </c>
       <c r="B554" t="s" s="2">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="C554" t="s" s="2">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="D554" s="2"/>
     </row>
@@ -11667,10 +11699,10 @@
         <v>58</v>
       </c>
       <c r="B555" t="s" s="2">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="C555" t="s" s="2">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="D555" s="2"/>
     </row>
@@ -11679,10 +11711,10 @@
         <v>58</v>
       </c>
       <c r="B556" t="s" s="2">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="C556" t="s" s="2">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="D556" s="2"/>
     </row>
@@ -11691,13 +11723,13 @@
         <v>58</v>
       </c>
       <c r="B557" t="s" s="2">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="C557" t="s" s="2">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="D557" t="s" s="2">
-        <v>1330</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="558">
@@ -11705,13 +11737,13 @@
         <v>58</v>
       </c>
       <c r="B558" t="s" s="2">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="C558" t="s" s="2">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="D558" t="s" s="2">
-        <v>1333</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="559">
@@ -11719,22 +11751,24 @@
         <v>58</v>
       </c>
       <c r="B559" t="s" s="2">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="C559" t="s" s="2">
-        <v>1335</v>
-      </c>
-      <c r="D559" s="2"/>
+        <v>1336</v>
+      </c>
+      <c r="D559" t="s" s="2">
+        <v>1337</v>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="s" s="2">
         <v>58</v>
       </c>
       <c r="B560" t="s" s="2">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="C560" t="s" s="2">
-        <v>1337</v>
+        <v>1339</v>
       </c>
       <c r="D560" s="2"/>
     </row>
@@ -11743,10 +11777,10 @@
         <v>58</v>
       </c>
       <c r="B561" t="s" s="2">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="C561" t="s" s="2">
-        <v>1339</v>
+        <v>1341</v>
       </c>
       <c r="D561" s="2"/>
     </row>
@@ -11755,10 +11789,10 @@
         <v>58</v>
       </c>
       <c r="B562" t="s" s="2">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="C562" t="s" s="2">
-        <v>1341</v>
+        <v>1343</v>
       </c>
       <c r="D562" s="2"/>
     </row>
@@ -11767,10 +11801,10 @@
         <v>58</v>
       </c>
       <c r="B563" t="s" s="2">
-        <v>1342</v>
+        <v>1344</v>
       </c>
       <c r="C563" t="s" s="2">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="D563" s="2"/>
     </row>
@@ -11779,10 +11813,10 @@
         <v>58</v>
       </c>
       <c r="B564" t="s" s="2">
-        <v>1344</v>
+        <v>1346</v>
       </c>
       <c r="C564" t="s" s="2">
-        <v>1345</v>
+        <v>1347</v>
       </c>
       <c r="D564" s="2"/>
     </row>
@@ -11791,10 +11825,10 @@
         <v>58</v>
       </c>
       <c r="B565" t="s" s="2">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="C565" t="s" s="2">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="D565" s="2"/>
     </row>
@@ -11803,10 +11837,10 @@
         <v>58</v>
       </c>
       <c r="B566" t="s" s="2">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="C566" t="s" s="2">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="D566" s="2"/>
     </row>
@@ -11815,10 +11849,10 @@
         <v>58</v>
       </c>
       <c r="B567" t="s" s="2">
-        <v>1350</v>
+        <v>1352</v>
       </c>
       <c r="C567" t="s" s="2">
-        <v>1351</v>
+        <v>1353</v>
       </c>
       <c r="D567" s="2"/>
     </row>
@@ -11827,10 +11861,10 @@
         <v>58</v>
       </c>
       <c r="B568" t="s" s="2">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="C568" t="s" s="2">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="D568" s="2"/>
     </row>
@@ -11839,10 +11873,10 @@
         <v>58</v>
       </c>
       <c r="B569" t="s" s="2">
-        <v>1354</v>
+        <v>1356</v>
       </c>
       <c r="C569" t="s" s="2">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="D569" s="2"/>
     </row>
@@ -11851,10 +11885,10 @@
         <v>58</v>
       </c>
       <c r="B570" t="s" s="2">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="C570" t="s" s="2">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="D570" s="2"/>
     </row>
@@ -11863,10 +11897,10 @@
         <v>58</v>
       </c>
       <c r="B571" t="s" s="2">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="C571" t="s" s="2">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="D571" s="2"/>
     </row>
@@ -11875,10 +11909,10 @@
         <v>58</v>
       </c>
       <c r="B572" t="s" s="2">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="C572" t="s" s="2">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="D572" s="2"/>
     </row>
@@ -11887,10 +11921,10 @@
         <v>58</v>
       </c>
       <c r="B573" t="s" s="2">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="C573" t="s" s="2">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="D573" s="2"/>
     </row>
@@ -11899,10 +11933,10 @@
         <v>58</v>
       </c>
       <c r="B574" t="s" s="2">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="C574" t="s" s="2">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="D574" s="2"/>
     </row>
@@ -11911,106 +11945,122 @@
         <v>58</v>
       </c>
       <c r="B575" t="s" s="2">
-        <v>1366</v>
+        <v>1368</v>
       </c>
       <c r="C575" t="s" s="2">
-        <v>1367</v>
-      </c>
-      <c r="D575" s="2"/>
+        <v>1369</v>
+      </c>
+      <c r="D575" t="s" s="2">
+        <v>1370</v>
+      </c>
     </row>
     <row r="576">
       <c r="A576" t="s" s="2">
         <v>58</v>
       </c>
       <c r="B576" t="s" s="2">
-        <v>1368</v>
+        <v>1371</v>
       </c>
       <c r="C576" t="s" s="2">
-        <v>1369</v>
-      </c>
-      <c r="D576" s="2"/>
+        <v>1372</v>
+      </c>
+      <c r="D576" t="s" s="2">
+        <v>1373</v>
+      </c>
     </row>
     <row r="577">
       <c r="A577" t="s" s="2">
         <v>58</v>
       </c>
       <c r="B577" t="s" s="2">
-        <v>1370</v>
+        <v>1374</v>
       </c>
       <c r="C577" t="s" s="2">
-        <v>1371</v>
-      </c>
-      <c r="D577" s="2"/>
+        <v>1375</v>
+      </c>
+      <c r="D577" t="s" s="2">
+        <v>1376</v>
+      </c>
     </row>
     <row r="578">
       <c r="A578" t="s" s="2">
         <v>58</v>
       </c>
       <c r="B578" t="s" s="2">
-        <v>1372</v>
+        <v>1377</v>
       </c>
       <c r="C578" t="s" s="2">
-        <v>1373</v>
-      </c>
-      <c r="D578" s="2"/>
+        <v>1378</v>
+      </c>
+      <c r="D578" t="s" s="2">
+        <v>1379</v>
+      </c>
     </row>
     <row r="579">
       <c r="A579" t="s" s="2">
         <v>58</v>
       </c>
       <c r="B579" t="s" s="2">
-        <v>1374</v>
+        <v>1380</v>
       </c>
       <c r="C579" t="s" s="2">
-        <v>1375</v>
-      </c>
-      <c r="D579" s="2"/>
+        <v>1381</v>
+      </c>
+      <c r="D579" t="s" s="2">
+        <v>1382</v>
+      </c>
     </row>
     <row r="580">
       <c r="A580" t="s" s="2">
         <v>58</v>
       </c>
       <c r="B580" t="s" s="2">
-        <v>1376</v>
+        <v>1383</v>
       </c>
       <c r="C580" t="s" s="2">
-        <v>1377</v>
-      </c>
-      <c r="D580" s="2"/>
+        <v>1384</v>
+      </c>
+      <c r="D580" t="s" s="2">
+        <v>1385</v>
+      </c>
     </row>
     <row r="581">
       <c r="A581" t="s" s="2">
         <v>58</v>
       </c>
       <c r="B581" t="s" s="2">
-        <v>1378</v>
+        <v>1386</v>
       </c>
       <c r="C581" t="s" s="2">
-        <v>1379</v>
-      </c>
-      <c r="D581" s="2"/>
+        <v>1387</v>
+      </c>
+      <c r="D581" t="s" s="2">
+        <v>1388</v>
+      </c>
     </row>
     <row r="582">
       <c r="A582" t="s" s="2">
         <v>58</v>
       </c>
       <c r="B582" t="s" s="2">
-        <v>1380</v>
+        <v>1389</v>
       </c>
       <c r="C582" t="s" s="2">
-        <v>1381</v>
-      </c>
-      <c r="D582" s="2"/>
+        <v>1390</v>
+      </c>
+      <c r="D582" t="s" s="2">
+        <v>1391</v>
+      </c>
     </row>
     <row r="583">
       <c r="A583" t="s" s="2">
         <v>58</v>
       </c>
       <c r="B583" t="s" s="2">
-        <v>1382</v>
+        <v>1392</v>
       </c>
       <c r="C583" t="s" s="2">
-        <v>1383</v>
+        <v>1393</v>
       </c>
       <c r="D583" s="2"/>
     </row>
@@ -12019,7 +12069,7 @@
         <v>58</v>
       </c>
       <c r="B584" t="s" s="2">
-        <v>1384</v>
+        <v>1394</v>
       </c>
       <c r="C584" t="s" s="2">
         <v>431</v>
@@ -12031,13 +12081,13 @@
         <v>58</v>
       </c>
       <c r="B585" t="s" s="2">
-        <v>1385</v>
+        <v>1395</v>
       </c>
       <c r="C585" t="s" s="2">
-        <v>1386</v>
+        <v>1396</v>
       </c>
       <c r="D585" t="s" s="2">
-        <v>1387</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="586">
@@ -12045,13 +12095,13 @@
         <v>58</v>
       </c>
       <c r="B586" t="s" s="2">
-        <v>1388</v>
+        <v>1398</v>
       </c>
       <c r="C586" t="s" s="2">
-        <v>1389</v>
+        <v>1399</v>
       </c>
       <c r="D586" t="s" s="2">
-        <v>1390</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="587">
@@ -12059,13 +12109,13 @@
         <v>58</v>
       </c>
       <c r="B587" t="s" s="2">
-        <v>1391</v>
+        <v>1401</v>
       </c>
       <c r="C587" t="s" s="2">
-        <v>1392</v>
+        <v>1402</v>
       </c>
       <c r="D587" t="s" s="2">
-        <v>1393</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="588">
@@ -12073,13 +12123,13 @@
         <v>58</v>
       </c>
       <c r="B588" t="s" s="2">
-        <v>1394</v>
+        <v>1404</v>
       </c>
       <c r="C588" t="s" s="2">
-        <v>1395</v>
+        <v>1405</v>
       </c>
       <c r="D588" t="s" s="2">
-        <v>1396</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="589">
@@ -12087,13 +12137,13 @@
         <v>58</v>
       </c>
       <c r="B589" t="s" s="2">
-        <v>1397</v>
+        <v>1407</v>
       </c>
       <c r="C589" t="s" s="2">
-        <v>1398</v>
+        <v>1408</v>
       </c>
       <c r="D589" t="s" s="2">
-        <v>1399</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="590">
@@ -12101,13 +12151,13 @@
         <v>58</v>
       </c>
       <c r="B590" t="s" s="2">
-        <v>1400</v>
+        <v>1410</v>
       </c>
       <c r="C590" t="s" s="2">
-        <v>1401</v>
+        <v>1411</v>
       </c>
       <c r="D590" t="s" s="2">
-        <v>1402</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="591">
@@ -12115,10 +12165,10 @@
         <v>58</v>
       </c>
       <c r="B591" t="s" s="2">
-        <v>1403</v>
+        <v>1413</v>
       </c>
       <c r="C591" t="s" s="2">
-        <v>1404</v>
+        <v>1414</v>
       </c>
       <c r="D591" s="2"/>
     </row>
@@ -12127,10 +12177,10 @@
         <v>58</v>
       </c>
       <c r="B592" t="s" s="2">
-        <v>1405</v>
+        <v>1415</v>
       </c>
       <c r="C592" t="s" s="2">
-        <v>1406</v>
+        <v>1416</v>
       </c>
       <c r="D592" s="2"/>
     </row>
@@ -12142,7 +12192,7 @@
         <v>34</v>
       </c>
       <c r="C593" t="s" s="2">
-        <v>1407</v>
+        <v>1417</v>
       </c>
       <c r="D593" s="2"/>
     </row>

--- a/ig/DM-JUILLET-2025/CodeSystem-TRE-R211-ActiviteOperationnelle.xlsx
+++ b/ig/DM-JUILLET-2025/CodeSystem-TRE-R211-ActiviteOperationnelle.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2040" uniqueCount="1418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2041" uniqueCount="1419">
   <si>
     <t>Property</t>
   </si>
@@ -2216,6 +2216,9 @@
   </si>
   <si>
     <t>Soutien à la parentalité et accompagnement familial</t>
+  </si>
+  <si>
+    <t>Ensemble d’actions visant à accompagner les parents dans leur rôle éducatif, affectif et social, en tenant compte des besoins spécifiques de l’enfant et du contexte familial en renforcant les compétences parentales, favorisant les relations parents-enfants, prévenant les difficultés éducatives ou relationnelles, soutenant les familles confrontées à des problématiques spécifiques (handicap, maladie, précarité, troubles du développement, etc.). Cette orientation est étayée par la réalisation de formations continues spécifiques auprès de cette population (appuyées de données probantes) et d’une expérience professionnelle.</t>
   </si>
   <si>
     <t>309</t>
@@ -8518,20 +8521,22 @@
       <c r="C309" t="s" s="2">
         <v>733</v>
       </c>
-      <c r="D309" s="2"/>
+      <c r="D309" t="s" s="2">
+        <v>734</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="s" s="2">
         <v>58</v>
       </c>
       <c r="B310" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C310" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="D310" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
     <row r="311">
@@ -8539,10 +8544,10 @@
         <v>58</v>
       </c>
       <c r="B311" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C311" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="D311" s="2"/>
     </row>
@@ -8551,10 +8556,10 @@
         <v>58</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C312" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D312" s="2"/>
     </row>
@@ -8563,13 +8568,13 @@
         <v>58</v>
       </c>
       <c r="B313" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C313" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="D313" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="314">
@@ -8577,13 +8582,13 @@
         <v>58</v>
       </c>
       <c r="B314" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C314" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="D314" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="315">
@@ -8591,10 +8596,10 @@
         <v>58</v>
       </c>
       <c r="B315" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C315" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="D315" s="2"/>
     </row>
@@ -8603,10 +8608,10 @@
         <v>58</v>
       </c>
       <c r="B316" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C316" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="D316" s="2"/>
     </row>
@@ -8615,10 +8620,10 @@
         <v>58</v>
       </c>
       <c r="B317" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C317" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="D317" s="2"/>
     </row>
@@ -8627,10 +8632,10 @@
         <v>58</v>
       </c>
       <c r="B318" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C318" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="D318" s="2"/>
     </row>
@@ -8639,10 +8644,10 @@
         <v>58</v>
       </c>
       <c r="B319" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C319" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="D319" s="2"/>
     </row>
@@ -8651,10 +8656,10 @@
         <v>58</v>
       </c>
       <c r="B320" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C320" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="D320" s="2"/>
     </row>
@@ -8663,10 +8668,10 @@
         <v>58</v>
       </c>
       <c r="B321" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C321" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="D321" s="2"/>
     </row>
@@ -8675,10 +8680,10 @@
         <v>58</v>
       </c>
       <c r="B322" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C322" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="D322" s="2"/>
     </row>
@@ -8687,13 +8692,13 @@
         <v>58</v>
       </c>
       <c r="B323" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C323" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D323" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
     <row r="324">
@@ -8701,10 +8706,10 @@
         <v>58</v>
       </c>
       <c r="B324" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C324" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D324" s="2"/>
     </row>
@@ -8713,10 +8718,10 @@
         <v>58</v>
       </c>
       <c r="B325" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C325" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="D325" s="2"/>
     </row>
@@ -8725,13 +8730,13 @@
         <v>58</v>
       </c>
       <c r="B326" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C326" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="D326" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="327">
@@ -8739,10 +8744,10 @@
         <v>58</v>
       </c>
       <c r="B327" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C327" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D327" s="2"/>
     </row>
@@ -8751,10 +8756,10 @@
         <v>58</v>
       </c>
       <c r="B328" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C328" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D328" s="2"/>
     </row>
@@ -8763,10 +8768,10 @@
         <v>58</v>
       </c>
       <c r="B329" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C329" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="D329" s="2"/>
     </row>
@@ -8775,10 +8780,10 @@
         <v>58</v>
       </c>
       <c r="B330" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C330" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="D330" s="2"/>
     </row>
@@ -8787,10 +8792,10 @@
         <v>58</v>
       </c>
       <c r="B331" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C331" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="D331" s="2"/>
     </row>
@@ -8799,10 +8804,10 @@
         <v>58</v>
       </c>
       <c r="B332" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C332" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D332" s="2"/>
     </row>
@@ -8811,10 +8816,10 @@
         <v>58</v>
       </c>
       <c r="B333" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C333" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="D333" s="2"/>
     </row>
@@ -8823,10 +8828,10 @@
         <v>58</v>
       </c>
       <c r="B334" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C334" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="D334" s="2"/>
     </row>
@@ -8835,13 +8840,13 @@
         <v>58</v>
       </c>
       <c r="B335" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C335" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="D335" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
     </row>
     <row r="336">
@@ -8849,13 +8854,13 @@
         <v>58</v>
       </c>
       <c r="B336" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C336" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D336" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
     </row>
     <row r="337">
@@ -8863,10 +8868,10 @@
         <v>58</v>
       </c>
       <c r="B337" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C337" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="D337" s="2"/>
     </row>
@@ -8875,10 +8880,10 @@
         <v>58</v>
       </c>
       <c r="B338" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C338" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="D338" s="2"/>
     </row>
@@ -8887,13 +8892,13 @@
         <v>58</v>
       </c>
       <c r="B339" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C339" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="D339" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
     </row>
     <row r="340">
@@ -8901,13 +8906,13 @@
         <v>58</v>
       </c>
       <c r="B340" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C340" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D340" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="341">
@@ -8915,13 +8920,13 @@
         <v>58</v>
       </c>
       <c r="B341" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C341" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D341" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
     </row>
     <row r="342">
@@ -8929,13 +8934,13 @@
         <v>58</v>
       </c>
       <c r="B342" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C342" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="D342" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="343">
@@ -8943,10 +8948,10 @@
         <v>58</v>
       </c>
       <c r="B343" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C343" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="D343" s="2"/>
     </row>
@@ -8955,10 +8960,10 @@
         <v>58</v>
       </c>
       <c r="B344" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C344" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D344" s="2"/>
     </row>
@@ -8967,10 +8972,10 @@
         <v>58</v>
       </c>
       <c r="B345" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C345" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D345" s="2"/>
     </row>
@@ -8979,10 +8984,10 @@
         <v>58</v>
       </c>
       <c r="B346" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C346" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="D346" s="2"/>
     </row>
@@ -8991,10 +8996,10 @@
         <v>58</v>
       </c>
       <c r="B347" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C347" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="D347" s="2"/>
     </row>
@@ -9003,13 +9008,13 @@
         <v>58</v>
       </c>
       <c r="B348" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C348" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D348" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="349">
@@ -9017,10 +9022,10 @@
         <v>58</v>
       </c>
       <c r="B349" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C349" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="D349" s="2"/>
     </row>
@@ -9029,13 +9034,13 @@
         <v>58</v>
       </c>
       <c r="B350" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C350" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="D350" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="351">
@@ -9043,10 +9048,10 @@
         <v>58</v>
       </c>
       <c r="B351" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C351" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D351" s="2"/>
     </row>
@@ -9055,10 +9060,10 @@
         <v>58</v>
       </c>
       <c r="B352" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C352" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="D352" s="2"/>
     </row>
@@ -9067,10 +9072,10 @@
         <v>58</v>
       </c>
       <c r="B353" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C353" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="D353" s="2"/>
     </row>
@@ -9079,10 +9084,10 @@
         <v>58</v>
       </c>
       <c r="B354" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="C354" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="D354" s="2"/>
     </row>
@@ -9091,10 +9096,10 @@
         <v>58</v>
       </c>
       <c r="B355" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="C355" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="D355" s="2"/>
     </row>
@@ -9103,10 +9108,10 @@
         <v>58</v>
       </c>
       <c r="B356" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="C356" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="D356" s="2"/>
     </row>
@@ -9115,10 +9120,10 @@
         <v>58</v>
       </c>
       <c r="B357" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C357" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="D357" s="2"/>
     </row>
@@ -9127,10 +9132,10 @@
         <v>58</v>
       </c>
       <c r="B358" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C358" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="D358" s="2"/>
     </row>
@@ -9139,10 +9144,10 @@
         <v>58</v>
       </c>
       <c r="B359" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C359" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="D359" s="2"/>
     </row>
@@ -9151,10 +9156,10 @@
         <v>58</v>
       </c>
       <c r="B360" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C360" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="D360" s="2"/>
     </row>
@@ -9163,10 +9168,10 @@
         <v>58</v>
       </c>
       <c r="B361" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C361" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="D361" s="2"/>
     </row>
@@ -9175,13 +9180,13 @@
         <v>58</v>
       </c>
       <c r="B362" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C362" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="D362" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
     </row>
     <row r="363">
@@ -9189,10 +9194,10 @@
         <v>58</v>
       </c>
       <c r="B363" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C363" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="D363" s="2"/>
     </row>
@@ -9201,10 +9206,10 @@
         <v>58</v>
       </c>
       <c r="B364" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C364" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="D364" s="2"/>
     </row>
@@ -9213,10 +9218,10 @@
         <v>58</v>
       </c>
       <c r="B365" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C365" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="D365" s="2"/>
     </row>
@@ -9225,10 +9230,10 @@
         <v>58</v>
       </c>
       <c r="B366" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C366" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="D366" s="2"/>
     </row>
@@ -9237,10 +9242,10 @@
         <v>58</v>
       </c>
       <c r="B367" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C367" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="D367" s="2"/>
     </row>
@@ -9249,13 +9254,13 @@
         <v>58</v>
       </c>
       <c r="B368" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C368" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="D368" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
     </row>
     <row r="369">
@@ -9263,10 +9268,10 @@
         <v>58</v>
       </c>
       <c r="B369" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C369" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="D369" s="2"/>
     </row>
@@ -9275,10 +9280,10 @@
         <v>58</v>
       </c>
       <c r="B370" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="C370" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="D370" s="2"/>
     </row>
@@ -9287,10 +9292,10 @@
         <v>58</v>
       </c>
       <c r="B371" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C371" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="D371" s="2"/>
     </row>
@@ -9299,10 +9304,10 @@
         <v>58</v>
       </c>
       <c r="B372" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C372" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="D372" s="2"/>
     </row>
@@ -9311,10 +9316,10 @@
         <v>58</v>
       </c>
       <c r="B373" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="C373" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="D373" s="2"/>
     </row>
@@ -9323,10 +9328,10 @@
         <v>58</v>
       </c>
       <c r="B374" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="C374" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="D374" s="2"/>
     </row>
@@ -9335,10 +9340,10 @@
         <v>58</v>
       </c>
       <c r="B375" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C375" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="D375" s="2"/>
     </row>
@@ -9347,10 +9352,10 @@
         <v>58</v>
       </c>
       <c r="B376" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="C376" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="D376" s="2"/>
     </row>
@@ -9359,10 +9364,10 @@
         <v>58</v>
       </c>
       <c r="B377" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="C377" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="D377" s="2"/>
     </row>
@@ -9371,10 +9376,10 @@
         <v>58</v>
       </c>
       <c r="B378" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C378" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="D378" s="2"/>
     </row>
@@ -9383,10 +9388,10 @@
         <v>58</v>
       </c>
       <c r="B379" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C379" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="D379" s="2"/>
     </row>
@@ -9395,10 +9400,10 @@
         <v>58</v>
       </c>
       <c r="B380" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="C380" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="D380" s="2"/>
     </row>
@@ -9407,10 +9412,10 @@
         <v>58</v>
       </c>
       <c r="B381" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C381" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="D381" s="2"/>
     </row>
@@ -9419,10 +9424,10 @@
         <v>58</v>
       </c>
       <c r="B382" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C382" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D382" s="2"/>
     </row>
@@ -9431,10 +9436,10 @@
         <v>58</v>
       </c>
       <c r="B383" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="C383" t="s" s="2">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="D383" s="2"/>
     </row>
@@ -9443,10 +9448,10 @@
         <v>58</v>
       </c>
       <c r="B384" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C384" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="D384" s="2"/>
     </row>
@@ -9455,10 +9460,10 @@
         <v>58</v>
       </c>
       <c r="B385" t="s" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C385" t="s" s="2">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="D385" s="2"/>
     </row>
@@ -9467,10 +9472,10 @@
         <v>58</v>
       </c>
       <c r="B386" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C386" t="s" s="2">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="D386" s="2"/>
     </row>
@@ -9479,10 +9484,10 @@
         <v>58</v>
       </c>
       <c r="B387" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C387" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="D387" s="2"/>
     </row>
@@ -9491,10 +9496,10 @@
         <v>58</v>
       </c>
       <c r="B388" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="C388" t="s" s="2">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="D388" s="2"/>
     </row>
@@ -9503,10 +9508,10 @@
         <v>58</v>
       </c>
       <c r="B389" t="s" s="2">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="C389" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="D389" s="2"/>
     </row>
@@ -9515,10 +9520,10 @@
         <v>58</v>
       </c>
       <c r="B390" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="C390" t="s" s="2">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="D390" s="2"/>
     </row>
@@ -9527,10 +9532,10 @@
         <v>58</v>
       </c>
       <c r="B391" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="C391" t="s" s="2">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="D391" s="2"/>
     </row>
@@ -9539,10 +9544,10 @@
         <v>58</v>
       </c>
       <c r="B392" t="s" s="2">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="C392" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="D392" s="2"/>
     </row>
@@ -9551,10 +9556,10 @@
         <v>58</v>
       </c>
       <c r="B393" t="s" s="2">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="C393" t="s" s="2">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="D393" s="2"/>
     </row>
@@ -9563,13 +9568,13 @@
         <v>58</v>
       </c>
       <c r="B394" t="s" s="2">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="C394" t="s" s="2">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="D394" t="s" s="2">
-        <v>917</v>
+        <v>918</v>
       </c>
     </row>
     <row r="395">
@@ -9577,13 +9582,13 @@
         <v>58</v>
       </c>
       <c r="B395" t="s" s="2">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="C395" t="s" s="2">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="D395" t="s" s="2">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="396">
@@ -9591,10 +9596,10 @@
         <v>58</v>
       </c>
       <c r="B396" t="s" s="2">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="C396" t="s" s="2">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="D396" s="2"/>
     </row>
@@ -9603,10 +9608,10 @@
         <v>58</v>
       </c>
       <c r="B397" t="s" s="2">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="C397" t="s" s="2">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D397" s="2"/>
     </row>
@@ -9615,13 +9620,13 @@
         <v>58</v>
       </c>
       <c r="B398" t="s" s="2">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="C398" t="s" s="2">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="D398" t="s" s="2">
-        <v>927</v>
+        <v>928</v>
       </c>
     </row>
     <row r="399">
@@ -9629,10 +9634,10 @@
         <v>58</v>
       </c>
       <c r="B399" t="s" s="2">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="C399" t="s" s="2">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="D399" s="2"/>
     </row>
@@ -9641,10 +9646,10 @@
         <v>58</v>
       </c>
       <c r="B400" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C400" t="s" s="2">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="D400" s="2"/>
     </row>
@@ -9653,10 +9658,10 @@
         <v>58</v>
       </c>
       <c r="B401" t="s" s="2">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C401" t="s" s="2">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="D401" s="2"/>
     </row>
@@ -9665,13 +9670,13 @@
         <v>58</v>
       </c>
       <c r="B402" t="s" s="2">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="C402" t="s" s="2">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="D402" t="s" s="2">
-        <v>936</v>
+        <v>937</v>
       </c>
     </row>
     <row r="403">
@@ -9679,13 +9684,13 @@
         <v>58</v>
       </c>
       <c r="B403" t="s" s="2">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="C403" t="s" s="2">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="D403" t="s" s="2">
-        <v>939</v>
+        <v>940</v>
       </c>
     </row>
     <row r="404">
@@ -9693,10 +9698,10 @@
         <v>58</v>
       </c>
       <c r="B404" t="s" s="2">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="C404" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="D404" s="2"/>
     </row>
@@ -9705,13 +9710,13 @@
         <v>58</v>
       </c>
       <c r="B405" t="s" s="2">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="C405" t="s" s="2">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="D405" t="s" s="2">
-        <v>944</v>
+        <v>945</v>
       </c>
     </row>
     <row r="406">
@@ -9719,10 +9724,10 @@
         <v>58</v>
       </c>
       <c r="B406" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="C406" t="s" s="2">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="D406" s="2"/>
     </row>
@@ -9731,10 +9736,10 @@
         <v>58</v>
       </c>
       <c r="B407" t="s" s="2">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="C407" t="s" s="2">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="D407" s="2"/>
     </row>
@@ -9743,10 +9748,10 @@
         <v>58</v>
       </c>
       <c r="B408" t="s" s="2">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C408" t="s" s="2">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="D408" s="2"/>
     </row>
@@ -9755,10 +9760,10 @@
         <v>58</v>
       </c>
       <c r="B409" t="s" s="2">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="C409" t="s" s="2">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="D409" s="2"/>
     </row>
@@ -9767,13 +9772,13 @@
         <v>58</v>
       </c>
       <c r="B410" t="s" s="2">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="C410" t="s" s="2">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="D410" t="s" s="2">
-        <v>955</v>
+        <v>956</v>
       </c>
     </row>
     <row r="411">
@@ -9781,13 +9786,13 @@
         <v>58</v>
       </c>
       <c r="B411" t="s" s="2">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="C411" t="s" s="2">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="D411" t="s" s="2">
-        <v>958</v>
+        <v>959</v>
       </c>
     </row>
     <row r="412">
@@ -9795,10 +9800,10 @@
         <v>58</v>
       </c>
       <c r="B412" t="s" s="2">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="C412" t="s" s="2">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="D412" s="2"/>
     </row>
@@ -9807,10 +9812,10 @@
         <v>58</v>
       </c>
       <c r="B413" t="s" s="2">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="C413" t="s" s="2">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="D413" s="2"/>
     </row>
@@ -9819,10 +9824,10 @@
         <v>58</v>
       </c>
       <c r="B414" t="s" s="2">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="C414" t="s" s="2">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="D414" s="2"/>
     </row>
@@ -9831,10 +9836,10 @@
         <v>58</v>
       </c>
       <c r="B415" t="s" s="2">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="C415" t="s" s="2">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="D415" s="2"/>
     </row>
@@ -9843,10 +9848,10 @@
         <v>58</v>
       </c>
       <c r="B416" t="s" s="2">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="C416" t="s" s="2">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="D416" s="2"/>
     </row>
@@ -9855,10 +9860,10 @@
         <v>58</v>
       </c>
       <c r="B417" t="s" s="2">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="C417" t="s" s="2">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="D417" s="2"/>
     </row>
@@ -9867,10 +9872,10 @@
         <v>58</v>
       </c>
       <c r="B418" t="s" s="2">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="C418" t="s" s="2">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="D418" s="2"/>
     </row>
@@ -9879,10 +9884,10 @@
         <v>58</v>
       </c>
       <c r="B419" t="s" s="2">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="C419" t="s" s="2">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="D419" s="2"/>
     </row>
@@ -9891,10 +9896,10 @@
         <v>58</v>
       </c>
       <c r="B420" t="s" s="2">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="C420" t="s" s="2">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="D420" s="2"/>
     </row>
@@ -9903,10 +9908,10 @@
         <v>58</v>
       </c>
       <c r="B421" t="s" s="2">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="C421" t="s" s="2">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="D421" s="2"/>
     </row>
@@ -9915,10 +9920,10 @@
         <v>58</v>
       </c>
       <c r="B422" t="s" s="2">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="C422" t="s" s="2">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="D422" s="2"/>
     </row>
@@ -9927,10 +9932,10 @@
         <v>58</v>
       </c>
       <c r="B423" t="s" s="2">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="C423" t="s" s="2">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="D423" s="2"/>
     </row>
@@ -9939,10 +9944,10 @@
         <v>58</v>
       </c>
       <c r="B424" t="s" s="2">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="C424" t="s" s="2">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="D424" s="2"/>
     </row>
@@ -9951,10 +9956,10 @@
         <v>58</v>
       </c>
       <c r="B425" t="s" s="2">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="C425" t="s" s="2">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="D425" s="2"/>
     </row>
@@ -9963,10 +9968,10 @@
         <v>58</v>
       </c>
       <c r="B426" t="s" s="2">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="C426" t="s" s="2">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="D426" s="2"/>
     </row>
@@ -9975,10 +9980,10 @@
         <v>58</v>
       </c>
       <c r="B427" t="s" s="2">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="C427" t="s" s="2">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="D427" s="2"/>
     </row>
@@ -9987,10 +9992,10 @@
         <v>58</v>
       </c>
       <c r="B428" t="s" s="2">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="C428" t="s" s="2">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="D428" s="2"/>
     </row>
@@ -9999,10 +10004,10 @@
         <v>58</v>
       </c>
       <c r="B429" t="s" s="2">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="C429" t="s" s="2">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="D429" s="2"/>
     </row>
@@ -10011,10 +10016,10 @@
         <v>58</v>
       </c>
       <c r="B430" t="s" s="2">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C430" t="s" s="2">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="D430" s="2"/>
     </row>
@@ -10023,10 +10028,10 @@
         <v>58</v>
       </c>
       <c r="B431" t="s" s="2">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="C431" t="s" s="2">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="D431" s="2"/>
     </row>
@@ -10035,10 +10040,10 @@
         <v>58</v>
       </c>
       <c r="B432" t="s" s="2">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="C432" t="s" s="2">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="D432" s="2"/>
     </row>
@@ -10047,10 +10052,10 @@
         <v>58</v>
       </c>
       <c r="B433" t="s" s="2">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="C433" t="s" s="2">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="D433" s="2"/>
     </row>
@@ -10059,10 +10064,10 @@
         <v>58</v>
       </c>
       <c r="B434" t="s" s="2">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="C434" t="s" s="2">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="D434" s="2"/>
     </row>
@@ -10071,13 +10076,13 @@
         <v>58</v>
       </c>
       <c r="B435" t="s" s="2">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C435" t="s" s="2">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="D435" t="s" s="2">
-        <v>1007</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="436">
@@ -10085,13 +10090,13 @@
         <v>58</v>
       </c>
       <c r="B436" t="s" s="2">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="C436" t="s" s="2">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="D436" t="s" s="2">
-        <v>1010</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="437">
@@ -10099,10 +10104,10 @@
         <v>58</v>
       </c>
       <c r="B437" t="s" s="2">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="C437" t="s" s="2">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="D437" s="2"/>
     </row>
@@ -10111,13 +10116,13 @@
         <v>58</v>
       </c>
       <c r="B438" t="s" s="2">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="C438" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D438" t="s" s="2">
-        <v>1015</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="439">
@@ -10125,10 +10130,10 @@
         <v>58</v>
       </c>
       <c r="B439" t="s" s="2">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="C439" t="s" s="2">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="D439" s="2"/>
     </row>
@@ -10137,13 +10142,13 @@
         <v>58</v>
       </c>
       <c r="B440" t="s" s="2">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="C440" t="s" s="2">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="D440" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="441">
@@ -10151,13 +10156,13 @@
         <v>58</v>
       </c>
       <c r="B441" t="s" s="2">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="C441" t="s" s="2">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="D441" t="s" s="2">
-        <v>1023</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="442">
@@ -10165,13 +10170,13 @@
         <v>58</v>
       </c>
       <c r="B442" t="s" s="2">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="C442" t="s" s="2">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="D442" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="443">
@@ -10179,13 +10184,13 @@
         <v>58</v>
       </c>
       <c r="B443" t="s" s="2">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="C443" t="s" s="2">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="D443" t="s" s="2">
-        <v>1029</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="444">
@@ -10193,13 +10198,13 @@
         <v>58</v>
       </c>
       <c r="B444" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="C444" t="s" s="2">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="D444" t="s" s="2">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="445">
@@ -10207,13 +10212,13 @@
         <v>58</v>
       </c>
       <c r="B445" t="s" s="2">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="C445" t="s" s="2">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="D445" t="s" s="2">
-        <v>1035</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="446">
@@ -10221,13 +10226,13 @@
         <v>58</v>
       </c>
       <c r="B446" t="s" s="2">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="C446" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="D446" t="s" s="2">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="447">
@@ -10235,13 +10240,13 @@
         <v>58</v>
       </c>
       <c r="B447" t="s" s="2">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="C447" t="s" s="2">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="D447" t="s" s="2">
-        <v>1041</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="448">
@@ -10249,13 +10254,13 @@
         <v>58</v>
       </c>
       <c r="B448" t="s" s="2">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C448" t="s" s="2">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="D448" t="s" s="2">
-        <v>1044</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="449">
@@ -10263,13 +10268,13 @@
         <v>58</v>
       </c>
       <c r="B449" t="s" s="2">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C449" t="s" s="2">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="D449" t="s" s="2">
-        <v>1047</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="450">
@@ -10277,13 +10282,13 @@
         <v>58</v>
       </c>
       <c r="B450" t="s" s="2">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="C450" t="s" s="2">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="D450" t="s" s="2">
-        <v>1050</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="451">
@@ -10291,13 +10296,13 @@
         <v>58</v>
       </c>
       <c r="B451" t="s" s="2">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="C451" t="s" s="2">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="D451" t="s" s="2">
-        <v>1053</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="452">
@@ -10305,13 +10310,13 @@
         <v>58</v>
       </c>
       <c r="B452" t="s" s="2">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="C452" t="s" s="2">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="D452" t="s" s="2">
-        <v>1056</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="453">
@@ -10319,13 +10324,13 @@
         <v>58</v>
       </c>
       <c r="B453" t="s" s="2">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C453" t="s" s="2">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="D453" t="s" s="2">
-        <v>1059</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="454">
@@ -10333,10 +10338,10 @@
         <v>58</v>
       </c>
       <c r="B454" t="s" s="2">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="C454" t="s" s="2">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="D454" s="2"/>
     </row>
@@ -10345,13 +10350,13 @@
         <v>58</v>
       </c>
       <c r="B455" t="s" s="2">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="C455" t="s" s="2">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="D455" t="s" s="2">
-        <v>1064</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="456">
@@ -10359,13 +10364,13 @@
         <v>58</v>
       </c>
       <c r="B456" t="s" s="2">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C456" t="s" s="2">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="D456" t="s" s="2">
-        <v>1067</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="457">
@@ -10373,13 +10378,13 @@
         <v>58</v>
       </c>
       <c r="B457" t="s" s="2">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="C457" t="s" s="2">
         <v>568</v>
       </c>
       <c r="D457" t="s" s="2">
-        <v>1069</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="458">
@@ -10387,10 +10392,10 @@
         <v>58</v>
       </c>
       <c r="B458" t="s" s="2">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="C458" t="s" s="2">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="D458" s="2"/>
     </row>
@@ -10399,7 +10404,7 @@
         <v>58</v>
       </c>
       <c r="B459" t="s" s="2">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="C459" t="s" s="2">
         <v>574</v>
@@ -10413,7 +10418,7 @@
         <v>58</v>
       </c>
       <c r="B460" t="s" s="2">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="C460" t="s" s="2">
         <v>571</v>
@@ -10427,10 +10432,10 @@
         <v>58</v>
       </c>
       <c r="B461" t="s" s="2">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="C461" t="s" s="2">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="D461" t="s" s="2">
         <v>572</v>
@@ -10441,7 +10446,7 @@
         <v>58</v>
       </c>
       <c r="B462" t="s" s="2">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="C462" t="s" s="2">
         <v>580</v>
@@ -10455,7 +10460,7 @@
         <v>58</v>
       </c>
       <c r="B463" t="s" s="2">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C463" t="s" s="2">
         <v>576</v>
@@ -10469,10 +10474,10 @@
         <v>58</v>
       </c>
       <c r="B464" t="s" s="2">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="C464" t="s" s="2">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="D464" t="s" s="2">
         <v>572</v>
@@ -10483,10 +10488,10 @@
         <v>58</v>
       </c>
       <c r="B465" t="s" s="2">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="C465" t="s" s="2">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="D465" t="s" s="2">
         <v>572</v>
@@ -10497,10 +10502,10 @@
         <v>58</v>
       </c>
       <c r="B466" t="s" s="2">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="C466" t="s" s="2">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="D466" t="s" s="2">
         <v>572</v>
@@ -10511,13 +10516,13 @@
         <v>58</v>
       </c>
       <c r="B467" t="s" s="2">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="C467" t="s" s="2">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="D467" t="s" s="2">
-        <v>1086</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="468">
@@ -10525,13 +10530,13 @@
         <v>58</v>
       </c>
       <c r="B468" t="s" s="2">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="C468" t="s" s="2">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="D468" t="s" s="2">
-        <v>1089</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="469">
@@ -10539,13 +10544,13 @@
         <v>58</v>
       </c>
       <c r="B469" t="s" s="2">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="C469" t="s" s="2">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="D469" t="s" s="2">
-        <v>1092</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="470">
@@ -10553,13 +10558,13 @@
         <v>58</v>
       </c>
       <c r="B470" t="s" s="2">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="C470" t="s" s="2">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="D470" t="s" s="2">
-        <v>1095</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="471">
@@ -10567,13 +10572,13 @@
         <v>58</v>
       </c>
       <c r="B471" t="s" s="2">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="C471" t="s" s="2">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="D471" t="s" s="2">
-        <v>1098</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="472">
@@ -10581,13 +10586,13 @@
         <v>58</v>
       </c>
       <c r="B472" t="s" s="2">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="C472" t="s" s="2">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="D472" t="s" s="2">
-        <v>1101</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="473">
@@ -10595,13 +10600,13 @@
         <v>58</v>
       </c>
       <c r="B473" t="s" s="2">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="C473" t="s" s="2">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="D473" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="474">
@@ -10609,13 +10614,13 @@
         <v>58</v>
       </c>
       <c r="B474" t="s" s="2">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="C474" t="s" s="2">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="D474" t="s" s="2">
-        <v>1107</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="475">
@@ -10623,13 +10628,13 @@
         <v>58</v>
       </c>
       <c r="B475" t="s" s="2">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="C475" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="D475" t="s" s="2">
-        <v>1110</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="476">
@@ -10637,13 +10642,13 @@
         <v>58</v>
       </c>
       <c r="B476" t="s" s="2">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="C476" t="s" s="2">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D476" t="s" s="2">
-        <v>1113</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="477">
@@ -10651,13 +10656,13 @@
         <v>58</v>
       </c>
       <c r="B477" t="s" s="2">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="C477" t="s" s="2">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D477" t="s" s="2">
-        <v>1116</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="478">
@@ -10665,13 +10670,13 @@
         <v>58</v>
       </c>
       <c r="B478" t="s" s="2">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="C478" t="s" s="2">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="D478" t="s" s="2">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="479">
@@ -10679,13 +10684,13 @@
         <v>58</v>
       </c>
       <c r="B479" t="s" s="2">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="C479" t="s" s="2">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D479" t="s" s="2">
-        <v>1122</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="480">
@@ -10693,13 +10698,13 @@
         <v>58</v>
       </c>
       <c r="B480" t="s" s="2">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="C480" t="s" s="2">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="D480" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="481">
@@ -10707,13 +10712,13 @@
         <v>58</v>
       </c>
       <c r="B481" t="s" s="2">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="C481" t="s" s="2">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="D481" t="s" s="2">
-        <v>1127</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="482">
@@ -10721,13 +10726,13 @@
         <v>58</v>
       </c>
       <c r="B482" t="s" s="2">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="C482" t="s" s="2">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="D482" t="s" s="2">
-        <v>1130</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="483">
@@ -10735,13 +10740,13 @@
         <v>58</v>
       </c>
       <c r="B483" t="s" s="2">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="C483" t="s" s="2">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="D483" t="s" s="2">
-        <v>1133</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="484">
@@ -10749,13 +10754,13 @@
         <v>58</v>
       </c>
       <c r="B484" t="s" s="2">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="C484" t="s" s="2">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="D484" t="s" s="2">
-        <v>1136</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="485">
@@ -10763,13 +10768,13 @@
         <v>58</v>
       </c>
       <c r="B485" t="s" s="2">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="C485" t="s" s="2">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="D485" t="s" s="2">
-        <v>1139</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="486">
@@ -10777,13 +10782,13 @@
         <v>58</v>
       </c>
       <c r="B486" t="s" s="2">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="C486" t="s" s="2">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="D486" t="s" s="2">
-        <v>1142</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="487">
@@ -10791,13 +10796,13 @@
         <v>58</v>
       </c>
       <c r="B487" t="s" s="2">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="C487" t="s" s="2">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="D487" t="s" s="2">
-        <v>1145</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="488">
@@ -10805,13 +10810,13 @@
         <v>58</v>
       </c>
       <c r="B488" t="s" s="2">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="C488" t="s" s="2">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="D488" t="s" s="2">
-        <v>1148</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="489">
@@ -10819,13 +10824,13 @@
         <v>58</v>
       </c>
       <c r="B489" t="s" s="2">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="C489" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="D489" t="s" s="2">
-        <v>1151</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="490">
@@ -10833,13 +10838,13 @@
         <v>58</v>
       </c>
       <c r="B490" t="s" s="2">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="C490" t="s" s="2">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="D490" t="s" s="2">
-        <v>1154</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="491">
@@ -10847,13 +10852,13 @@
         <v>58</v>
       </c>
       <c r="B491" t="s" s="2">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="C491" t="s" s="2">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="D491" t="s" s="2">
-        <v>1157</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="492">
@@ -10861,10 +10866,10 @@
         <v>58</v>
       </c>
       <c r="B492" t="s" s="2">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="C492" t="s" s="2">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="D492" s="2"/>
     </row>
@@ -10873,13 +10878,13 @@
         <v>58</v>
       </c>
       <c r="B493" t="s" s="2">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="C493" t="s" s="2">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="D493" t="s" s="2">
-        <v>1162</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="494">
@@ -10887,13 +10892,13 @@
         <v>58</v>
       </c>
       <c r="B494" t="s" s="2">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="C494" t="s" s="2">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="D494" t="s" s="2">
-        <v>1165</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="495">
@@ -10901,13 +10906,13 @@
         <v>58</v>
       </c>
       <c r="B495" t="s" s="2">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="C495" t="s" s="2">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="D495" t="s" s="2">
-        <v>1168</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="496">
@@ -10915,13 +10920,13 @@
         <v>58</v>
       </c>
       <c r="B496" t="s" s="2">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="C496" t="s" s="2">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="D496" t="s" s="2">
-        <v>1171</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="497">
@@ -10929,13 +10934,13 @@
         <v>58</v>
       </c>
       <c r="B497" t="s" s="2">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="C497" t="s" s="2">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="D497" t="s" s="2">
-        <v>1174</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="498">
@@ -10943,13 +10948,13 @@
         <v>58</v>
       </c>
       <c r="B498" t="s" s="2">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="C498" t="s" s="2">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="D498" t="s" s="2">
-        <v>1177</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="499">
@@ -10957,13 +10962,13 @@
         <v>58</v>
       </c>
       <c r="B499" t="s" s="2">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="C499" t="s" s="2">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="D499" t="s" s="2">
-        <v>1180</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="500">
@@ -10971,10 +10976,10 @@
         <v>58</v>
       </c>
       <c r="B500" t="s" s="2">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="C500" t="s" s="2">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="D500" s="2"/>
     </row>
@@ -10983,13 +10988,13 @@
         <v>58</v>
       </c>
       <c r="B501" t="s" s="2">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="C501" t="s" s="2">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="D501" t="s" s="2">
-        <v>1185</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="502">
@@ -10997,13 +11002,13 @@
         <v>58</v>
       </c>
       <c r="B502" t="s" s="2">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="C502" t="s" s="2">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="D502" t="s" s="2">
-        <v>1188</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="503">
@@ -11011,13 +11016,13 @@
         <v>58</v>
       </c>
       <c r="B503" t="s" s="2">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C503" t="s" s="2">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="D503" t="s" s="2">
-        <v>1191</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="504">
@@ -11025,13 +11030,13 @@
         <v>58</v>
       </c>
       <c r="B504" t="s" s="2">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="C504" t="s" s="2">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="D504" t="s" s="2">
-        <v>1194</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="505">
@@ -11039,13 +11044,13 @@
         <v>58</v>
       </c>
       <c r="B505" t="s" s="2">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="C505" t="s" s="2">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="D505" t="s" s="2">
-        <v>1197</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="506">
@@ -11053,13 +11058,13 @@
         <v>58</v>
       </c>
       <c r="B506" t="s" s="2">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="C506" t="s" s="2">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="D506" t="s" s="2">
-        <v>1200</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="507">
@@ -11067,13 +11072,13 @@
         <v>58</v>
       </c>
       <c r="B507" t="s" s="2">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="C507" t="s" s="2">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="D507" t="s" s="2">
-        <v>1203</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="508">
@@ -11081,13 +11086,13 @@
         <v>58</v>
       </c>
       <c r="B508" t="s" s="2">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="C508" t="s" s="2">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="D508" t="s" s="2">
-        <v>1206</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="509">
@@ -11095,13 +11100,13 @@
         <v>58</v>
       </c>
       <c r="B509" t="s" s="2">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="C509" t="s" s="2">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="D509" t="s" s="2">
-        <v>1209</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="510">
@@ -11109,13 +11114,13 @@
         <v>58</v>
       </c>
       <c r="B510" t="s" s="2">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="C510" t="s" s="2">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="D510" t="s" s="2">
-        <v>1212</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="511">
@@ -11123,13 +11128,13 @@
         <v>58</v>
       </c>
       <c r="B511" t="s" s="2">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="C511" t="s" s="2">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="D511" t="s" s="2">
-        <v>1215</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="512">
@@ -11137,13 +11142,13 @@
         <v>58</v>
       </c>
       <c r="B512" t="s" s="2">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="C512" t="s" s="2">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="D512" t="s" s="2">
-        <v>1218</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="513">
@@ -11151,13 +11156,13 @@
         <v>58</v>
       </c>
       <c r="B513" t="s" s="2">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="C513" t="s" s="2">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="D513" t="s" s="2">
-        <v>1221</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="514">
@@ -11165,10 +11170,10 @@
         <v>58</v>
       </c>
       <c r="B514" t="s" s="2">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="C514" t="s" s="2">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="D514" s="2"/>
     </row>
@@ -11177,10 +11182,10 @@
         <v>58</v>
       </c>
       <c r="B515" t="s" s="2">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="C515" t="s" s="2">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="D515" s="2"/>
     </row>
@@ -11189,10 +11194,10 @@
         <v>58</v>
       </c>
       <c r="B516" t="s" s="2">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="C516" t="s" s="2">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="D516" s="2"/>
     </row>
@@ -11201,10 +11206,10 @@
         <v>58</v>
       </c>
       <c r="B517" t="s" s="2">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="C517" t="s" s="2">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="D517" s="2"/>
     </row>
@@ -11213,10 +11218,10 @@
         <v>58</v>
       </c>
       <c r="B518" t="s" s="2">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="C518" t="s" s="2">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="D518" s="2"/>
     </row>
@@ -11225,10 +11230,10 @@
         <v>58</v>
       </c>
       <c r="B519" t="s" s="2">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="C519" t="s" s="2">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="D519" s="2"/>
     </row>
@@ -11237,13 +11242,13 @@
         <v>58</v>
       </c>
       <c r="B520" t="s" s="2">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="C520" t="s" s="2">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="D520" t="s" s="2">
-        <v>1236</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="521">
@@ -11251,13 +11256,13 @@
         <v>58</v>
       </c>
       <c r="B521" t="s" s="2">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="C521" t="s" s="2">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="D521" t="s" s="2">
-        <v>1239</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="522">
@@ -11265,10 +11270,10 @@
         <v>58</v>
       </c>
       <c r="B522" t="s" s="2">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="C522" t="s" s="2">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="D522" s="2"/>
     </row>
@@ -11277,13 +11282,13 @@
         <v>58</v>
       </c>
       <c r="B523" t="s" s="2">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="C523" t="s" s="2">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="D523" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="524">
@@ -11291,10 +11296,10 @@
         <v>58</v>
       </c>
       <c r="B524" t="s" s="2">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="C524" t="s" s="2">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="D524" s="2"/>
     </row>
@@ -11303,10 +11308,10 @@
         <v>58</v>
       </c>
       <c r="B525" t="s" s="2">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="C525" t="s" s="2">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="D525" s="2"/>
     </row>
@@ -11315,10 +11320,10 @@
         <v>58</v>
       </c>
       <c r="B526" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="C526" t="s" s="2">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="D526" s="2"/>
     </row>
@@ -11327,10 +11332,10 @@
         <v>58</v>
       </c>
       <c r="B527" t="s" s="2">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="C527" t="s" s="2">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="D527" s="2"/>
     </row>
@@ -11339,13 +11344,13 @@
         <v>58</v>
       </c>
       <c r="B528" t="s" s="2">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="C528" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="D528" t="s" s="2">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="529">
@@ -11353,13 +11358,13 @@
         <v>58</v>
       </c>
       <c r="B529" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="C529" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="D529" t="s" s="2">
-        <v>1258</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="530">
@@ -11367,13 +11372,13 @@
         <v>58</v>
       </c>
       <c r="B530" t="s" s="2">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="C530" t="s" s="2">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="D530" t="s" s="2">
-        <v>1261</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="531">
@@ -11381,13 +11386,13 @@
         <v>58</v>
       </c>
       <c r="B531" t="s" s="2">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="C531" t="s" s="2">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="D531" t="s" s="2">
-        <v>1264</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="532">
@@ -11395,13 +11400,13 @@
         <v>58</v>
       </c>
       <c r="B532" t="s" s="2">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="C532" t="s" s="2">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="D532" t="s" s="2">
-        <v>1267</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="533">
@@ -11409,13 +11414,13 @@
         <v>58</v>
       </c>
       <c r="B533" t="s" s="2">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="C533" t="s" s="2">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="D533" t="s" s="2">
-        <v>1270</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="534">
@@ -11423,10 +11428,10 @@
         <v>58</v>
       </c>
       <c r="B534" t="s" s="2">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="C534" t="s" s="2">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="D534" s="2"/>
     </row>
@@ -11435,10 +11440,10 @@
         <v>58</v>
       </c>
       <c r="B535" t="s" s="2">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="C535" t="s" s="2">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="D535" s="2"/>
     </row>
@@ -11447,13 +11452,13 @@
         <v>58</v>
       </c>
       <c r="B536" t="s" s="2">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="C536" t="s" s="2">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="D536" t="s" s="2">
-        <v>1277</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="537">
@@ -11461,13 +11466,13 @@
         <v>58</v>
       </c>
       <c r="B537" t="s" s="2">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="C537" t="s" s="2">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="D537" t="s" s="2">
-        <v>1280</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="538">
@@ -11475,13 +11480,13 @@
         <v>58</v>
       </c>
       <c r="B538" t="s" s="2">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C538" t="s" s="2">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="D538" t="s" s="2">
-        <v>1283</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="539">
@@ -11489,13 +11494,13 @@
         <v>58</v>
       </c>
       <c r="B539" t="s" s="2">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C539" t="s" s="2">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="D539" t="s" s="2">
-        <v>1286</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="540">
@@ -11503,13 +11508,13 @@
         <v>58</v>
       </c>
       <c r="B540" t="s" s="2">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="C540" t="s" s="2">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="D540" t="s" s="2">
-        <v>1289</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="541">
@@ -11517,13 +11522,13 @@
         <v>58</v>
       </c>
       <c r="B541" t="s" s="2">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="C541" t="s" s="2">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="D541" t="s" s="2">
-        <v>1292</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="542">
@@ -11531,13 +11536,13 @@
         <v>58</v>
       </c>
       <c r="B542" t="s" s="2">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="C542" t="s" s="2">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="D542" t="s" s="2">
-        <v>1295</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="543">
@@ -11545,13 +11550,13 @@
         <v>58</v>
       </c>
       <c r="B543" t="s" s="2">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="C543" t="s" s="2">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="D543" t="s" s="2">
-        <v>1298</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="544">
@@ -11559,13 +11564,13 @@
         <v>58</v>
       </c>
       <c r="B544" t="s" s="2">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="C544" t="s" s="2">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="D544" t="s" s="2">
-        <v>1301</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="545">
@@ -11573,13 +11578,13 @@
         <v>58</v>
       </c>
       <c r="B545" t="s" s="2">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="C545" t="s" s="2">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="D545" t="s" s="2">
-        <v>1304</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="546">
@@ -11587,10 +11592,10 @@
         <v>58</v>
       </c>
       <c r="B546" t="s" s="2">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="C546" t="s" s="2">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="D546" s="2"/>
     </row>
@@ -11599,13 +11604,13 @@
         <v>58</v>
       </c>
       <c r="B547" t="s" s="2">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="C547" t="s" s="2">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="D547" t="s" s="2">
-        <v>1309</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="548">
@@ -11613,10 +11618,10 @@
         <v>58</v>
       </c>
       <c r="B548" t="s" s="2">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="C548" t="s" s="2">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="D548" s="2"/>
     </row>
@@ -11625,10 +11630,10 @@
         <v>58</v>
       </c>
       <c r="B549" t="s" s="2">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="C549" t="s" s="2">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="D549" s="2"/>
     </row>
@@ -11637,13 +11642,13 @@
         <v>58</v>
       </c>
       <c r="B550" t="s" s="2">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="C550" t="s" s="2">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="D550" t="s" s="2">
-        <v>1316</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="551">
@@ -11651,10 +11656,10 @@
         <v>58</v>
       </c>
       <c r="B551" t="s" s="2">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="C551" t="s" s="2">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="D551" s="2"/>
     </row>
@@ -11663,10 +11668,10 @@
         <v>58</v>
       </c>
       <c r="B552" t="s" s="2">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="C552" t="s" s="2">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="D552" s="2"/>
     </row>
@@ -11675,10 +11680,10 @@
         <v>58</v>
       </c>
       <c r="B553" t="s" s="2">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="C553" t="s" s="2">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="D553" s="2"/>
     </row>
@@ -11687,10 +11692,10 @@
         <v>58</v>
       </c>
       <c r="B554" t="s" s="2">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="C554" t="s" s="2">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="D554" s="2"/>
     </row>
@@ -11699,10 +11704,10 @@
         <v>58</v>
       </c>
       <c r="B555" t="s" s="2">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="C555" t="s" s="2">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="D555" s="2"/>
     </row>
@@ -11711,10 +11716,10 @@
         <v>58</v>
       </c>
       <c r="B556" t="s" s="2">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="C556" t="s" s="2">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="D556" s="2"/>
     </row>
@@ -11723,13 +11728,13 @@
         <v>58</v>
       </c>
       <c r="B557" t="s" s="2">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="C557" t="s" s="2">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="D557" t="s" s="2">
-        <v>1331</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="558">
@@ -11737,13 +11742,13 @@
         <v>58</v>
       </c>
       <c r="B558" t="s" s="2">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="C558" t="s" s="2">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="D558" t="s" s="2">
-        <v>1334</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="559">
@@ -11751,13 +11756,13 @@
         <v>58</v>
       </c>
       <c r="B559" t="s" s="2">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="C559" t="s" s="2">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="D559" t="s" s="2">
-        <v>1337</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="560">
@@ -11765,10 +11770,10 @@
         <v>58</v>
       </c>
       <c r="B560" t="s" s="2">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="C560" t="s" s="2">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="D560" s="2"/>
     </row>
@@ -11777,10 +11782,10 @@
         <v>58</v>
       </c>
       <c r="B561" t="s" s="2">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="C561" t="s" s="2">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="D561" s="2"/>
     </row>
@@ -11789,10 +11794,10 @@
         <v>58</v>
       </c>
       <c r="B562" t="s" s="2">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="C562" t="s" s="2">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="D562" s="2"/>
     </row>
@@ -11801,10 +11806,10 @@
         <v>58</v>
       </c>
       <c r="B563" t="s" s="2">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="C563" t="s" s="2">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="D563" s="2"/>
     </row>
@@ -11813,10 +11818,10 @@
         <v>58</v>
       </c>
       <c r="B564" t="s" s="2">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="C564" t="s" s="2">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="D564" s="2"/>
     </row>
@@ -11825,10 +11830,10 @@
         <v>58</v>
       </c>
       <c r="B565" t="s" s="2">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="C565" t="s" s="2">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="D565" s="2"/>
     </row>
@@ -11837,10 +11842,10 @@
         <v>58</v>
       </c>
       <c r="B566" t="s" s="2">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="C566" t="s" s="2">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="D566" s="2"/>
     </row>
@@ -11849,10 +11854,10 @@
         <v>58</v>
       </c>
       <c r="B567" t="s" s="2">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="C567" t="s" s="2">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="D567" s="2"/>
     </row>
@@ -11861,10 +11866,10 @@
         <v>58</v>
       </c>
       <c r="B568" t="s" s="2">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="C568" t="s" s="2">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="D568" s="2"/>
     </row>
@@ -11873,10 +11878,10 @@
         <v>58</v>
       </c>
       <c r="B569" t="s" s="2">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="C569" t="s" s="2">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="D569" s="2"/>
     </row>
@@ -11885,10 +11890,10 @@
         <v>58</v>
       </c>
       <c r="B570" t="s" s="2">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="C570" t="s" s="2">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="D570" s="2"/>
     </row>
@@ -11897,10 +11902,10 @@
         <v>58</v>
       </c>
       <c r="B571" t="s" s="2">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="C571" t="s" s="2">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="D571" s="2"/>
     </row>
@@ -11909,10 +11914,10 @@
         <v>58</v>
       </c>
       <c r="B572" t="s" s="2">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="C572" t="s" s="2">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="D572" s="2"/>
     </row>
@@ -11921,10 +11926,10 @@
         <v>58</v>
       </c>
       <c r="B573" t="s" s="2">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="C573" t="s" s="2">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="D573" s="2"/>
     </row>
@@ -11933,10 +11938,10 @@
         <v>58</v>
       </c>
       <c r="B574" t="s" s="2">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="C574" t="s" s="2">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="D574" s="2"/>
     </row>
@@ -11945,13 +11950,13 @@
         <v>58</v>
       </c>
       <c r="B575" t="s" s="2">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="C575" t="s" s="2">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="D575" t="s" s="2">
-        <v>1370</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="576">
@@ -11959,13 +11964,13 @@
         <v>58</v>
       </c>
       <c r="B576" t="s" s="2">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="C576" t="s" s="2">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="D576" t="s" s="2">
-        <v>1373</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="577">
@@ -11973,13 +11978,13 @@
         <v>58</v>
       </c>
       <c r="B577" t="s" s="2">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="C577" t="s" s="2">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="D577" t="s" s="2">
-        <v>1376</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="578">
@@ -11987,13 +11992,13 @@
         <v>58</v>
       </c>
       <c r="B578" t="s" s="2">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="C578" t="s" s="2">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="D578" t="s" s="2">
-        <v>1379</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="579">
@@ -12001,13 +12006,13 @@
         <v>58</v>
       </c>
       <c r="B579" t="s" s="2">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="C579" t="s" s="2">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="D579" t="s" s="2">
-        <v>1382</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="580">
@@ -12015,13 +12020,13 @@
         <v>58</v>
       </c>
       <c r="B580" t="s" s="2">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="C580" t="s" s="2">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="D580" t="s" s="2">
-        <v>1385</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="581">
@@ -12029,13 +12034,13 @@
         <v>58</v>
       </c>
       <c r="B581" t="s" s="2">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="C581" t="s" s="2">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="D581" t="s" s="2">
-        <v>1388</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="582">
@@ -12043,13 +12048,13 @@
         <v>58</v>
       </c>
       <c r="B582" t="s" s="2">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="C582" t="s" s="2">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="D582" t="s" s="2">
-        <v>1391</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="583">
@@ -12057,10 +12062,10 @@
         <v>58</v>
       </c>
       <c r="B583" t="s" s="2">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="C583" t="s" s="2">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="D583" s="2"/>
     </row>
@@ -12069,7 +12074,7 @@
         <v>58</v>
       </c>
       <c r="B584" t="s" s="2">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="C584" t="s" s="2">
         <v>431</v>
@@ -12081,13 +12086,13 @@
         <v>58</v>
       </c>
       <c r="B585" t="s" s="2">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="C585" t="s" s="2">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="D585" t="s" s="2">
-        <v>1397</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="586">
@@ -12095,13 +12100,13 @@
         <v>58</v>
       </c>
       <c r="B586" t="s" s="2">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="C586" t="s" s="2">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="D586" t="s" s="2">
-        <v>1400</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="587">
@@ -12109,13 +12114,13 @@
         <v>58</v>
       </c>
       <c r="B587" t="s" s="2">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="C587" t="s" s="2">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="D587" t="s" s="2">
-        <v>1403</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="588">
@@ -12123,13 +12128,13 @@
         <v>58</v>
       </c>
       <c r="B588" t="s" s="2">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="C588" t="s" s="2">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="D588" t="s" s="2">
-        <v>1406</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="589">
@@ -12137,13 +12142,13 @@
         <v>58</v>
       </c>
       <c r="B589" t="s" s="2">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="C589" t="s" s="2">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="D589" t="s" s="2">
-        <v>1409</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="590">
@@ -12151,13 +12156,13 @@
         <v>58</v>
       </c>
       <c r="B590" t="s" s="2">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="C590" t="s" s="2">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="D590" t="s" s="2">
-        <v>1412</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="591">
@@ -12165,10 +12170,10 @@
         <v>58</v>
       </c>
       <c r="B591" t="s" s="2">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="C591" t="s" s="2">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="D591" s="2"/>
     </row>
@@ -12177,10 +12182,10 @@
         <v>58</v>
       </c>
       <c r="B592" t="s" s="2">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="C592" t="s" s="2">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="D592" s="2"/>
     </row>
@@ -12192,7 +12197,7 @@
         <v>34</v>
       </c>
       <c r="C593" t="s" s="2">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="D593" s="2"/>
     </row>
